--- a/Assets/@Resources/Data/Excel/DialogueData.xlsx
+++ b/Assets/@Resources/Data/Excel/DialogueData.xlsx
@@ -14,6 +14,30 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GuildQuest2Text" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GuildQuest3Text" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GuildOnQuestText" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GuildQuest4Text" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GuildQuest5Text" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GuildQuest6Text" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GuildQuest7Text" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GuildQuest8Text" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GuildQuest9Text" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GuildQuest10Text" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GuildQuest11Text" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GuildQuest12Text" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GuildQuest13Text" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GuildQuest14Text" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GuildQuest15Text" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GuildQuest16Text" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GuildQuest17Text" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GuildQuest18Text" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GuildQuest19Text" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GuildQuest20Text" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GuildQuest21Text" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GuildQuest22Text" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GuildQuest23Text" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GuildQuest24Text" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GuildQuest25Text" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GuildQuest26Text" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GuildQuest27Text" sheetId="31" state="visible" r:id="rId31"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -512,6 +536,1216 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>TextKey</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Kor</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Eng</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>다시 오셨군요,
+[&lt;#2DFF00&gt;&lt;b&gt;까마귀 깃털&lt;/b&gt;&lt;/color&gt;] &lt;#2DFF00&gt;&lt;b&gt;5&lt;/b&gt;&lt;/color&gt;개는 구해오셨나요?</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Back again.
+Did you bring &lt;color=#2DFF00&gt;&lt;b&gt;5&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;까마귀 깃털&lt;/b&gt;&lt;/color&gt;?</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>….
+확인 되었습니다.
+협회 규정에 따라
+&lt;#00B9FF&gt;[&lt;#858585&gt;5&lt;/color&gt;]급 모험가&lt;/color&gt; 승급을 진행하겠습니다.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>...Confirmed.
+In accordance with guild regulations,
+your promotion to a &lt;color=#00B9FF&gt;[&lt;color=#858585&gt;5&lt;/color&gt;]-rank Adventurer&lt;/color&gt; will now proceed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>&lt;#00B9FF&gt;[&lt;#858585&gt;5&lt;/color&gt;]급 통행증&lt;/color&gt;을 새로 발급해 드렸습니다.
+이제 [&lt;#B0FF06&gt;텅 빈 굴&lt;/color&gt;]까지 출입하실 수 있습니다.
+권장 수준은 &lt;#FFFF00&gt;49&lt;/color&gt; 이상입니다.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>A new &lt;color=#00B9FF&gt;Rank 5 Permit&lt;/color&gt; has been issued.
+You may now enter &lt;color=#B0FF06&gt;텅 빈 굴&lt;/color&gt;.
+Recommended level: &lt;color=#FFFF00&gt;49&lt;/color&gt; or higher.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>다음 &lt;#00B9FF&gt;[&lt;#858585&gt;6&lt;/color&gt;]급&lt;/color&gt;으로 진급하시려면
+[&lt;#2DFF00&gt;&lt;b&gt;슬라임 젤리&lt;/b&gt;&lt;/color&gt;] &lt;#2DFF00&gt;&lt;b&gt;7&lt;/b&gt;&lt;/color&gt;개가 필요합니다.
+[&lt;#B0FF06&gt;텅 빈 굴&lt;/color&gt;]에 서식하는 마물에게서 얻으실 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>To reach &lt;color=#00B9FF&gt;rank 6&lt;/color&gt;,
+you will need &lt;color=#2DFF00&gt;&lt;b&gt;7&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;슬라임 젤리&lt;/b&gt;&lt;/color&gt;.
+They drop from the creatures of &lt;color=#B0FF06&gt;텅 빈 굴&lt;/color&gt;.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>그럼 다녀오신 뒤에 다시 뵙죠.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Then I’ll see you when you return.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>TextKey</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Kor</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Eng</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>다시 오셨군요,
+[&lt;#2DFF00&gt;&lt;b&gt;슬라임 젤리&lt;/b&gt;&lt;/color&gt;] &lt;#2DFF00&gt;&lt;b&gt;7&lt;/b&gt;&lt;/color&gt;개는 구해오셨나요?</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Back again.
+Did you bring &lt;color=#2DFF00&gt;&lt;b&gt;7&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;슬라임 젤리&lt;/b&gt;&lt;/color&gt;?</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>….
+확인 되었습니다.
+협회 규정에 따라
+&lt;#00B9FF&gt;[&lt;#858585&gt;6&lt;/color&gt;]급 모험가&lt;/color&gt; 승급을 진행하겠습니다.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>...Confirmed.
+In accordance with guild regulations,
+your promotion to a &lt;color=#00B9FF&gt;[&lt;color=#858585&gt;6&lt;/color&gt;]-rank Adventurer&lt;/color&gt; will now proceed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>&lt;#00B9FF&gt;[&lt;#858585&gt;6&lt;/color&gt;]급 통행증&lt;/color&gt;을 새로 발급해 드렸습니다.
+이제 [&lt;#B0FF06&gt;소금 늪지&lt;/color&gt;]까지 출입하실 수 있습니다.
+권장 수준은 &lt;#FFFF00&gt;61&lt;/color&gt; 이상입니다.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>A new &lt;color=#00B9FF&gt;Rank 6 Permit&lt;/color&gt; has been issued.
+You may now enter &lt;color=#B0FF06&gt;소금 늪지&lt;/color&gt;.
+Recommended level: &lt;color=#FFFF00&gt;61&lt;/color&gt; or higher.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>다음 &lt;#00B9FF&gt;[&lt;#858585&gt;7&lt;/color&gt;]급&lt;/color&gt;으로 진급하시려면
+[&lt;#2DFF00&gt;&lt;b&gt;늑대 송곳니&lt;/b&gt;&lt;/color&gt;] &lt;#2DFF00&gt;&lt;b&gt;9&lt;/b&gt;&lt;/color&gt;개가 필요합니다.
+[&lt;#B0FF06&gt;소금 늪지&lt;/color&gt;]에 서식하는 마물에게서 얻으실 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>To reach &lt;color=#00B9FF&gt;rank 7&lt;/color&gt;,
+you will need &lt;color=#2DFF00&gt;&lt;b&gt;9&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;늑대 송곳니&lt;/b&gt;&lt;/color&gt;.
+They drop from the creatures of &lt;color=#B0FF06&gt;소금 늪지&lt;/color&gt;.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>그럼 다녀오신 뒤에 다시 뵙죠.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Then I’ll see you when you return.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>TextKey</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Kor</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Eng</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>다시 오셨군요,
+[&lt;#2DFF00&gt;&lt;b&gt;늑대 송곳니&lt;/b&gt;&lt;/color&gt;] &lt;#2DFF00&gt;&lt;b&gt;9&lt;/b&gt;&lt;/color&gt;개는 구해오셨나요?</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Back again.
+Did you bring &lt;color=#2DFF00&gt;&lt;b&gt;9&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;늑대 송곳니&lt;/b&gt;&lt;/color&gt;?</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>….
+확인 되었습니다.
+협회 규정에 따라
+&lt;#00B9FF&gt;[&lt;#858585&gt;7&lt;/color&gt;]급 모험가&lt;/color&gt; 승급을 진행하겠습니다.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>...Confirmed.
+In accordance with guild regulations,
+your promotion to a &lt;color=#00B9FF&gt;[&lt;color=#858585&gt;7&lt;/color&gt;]-rank Adventurer&lt;/color&gt; will now proceed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>&lt;#00B9FF&gt;[&lt;#858585&gt;7&lt;/color&gt;]급 통행증&lt;/color&gt;을 새로 발급해 드렸습니다.
+이제 [&lt;#B0FF06&gt;밀물 동굴&lt;/color&gt;]까지 출입하실 수 있습니다.
+권장 수준은 &lt;#FFFF00&gt;73&lt;/color&gt; 이상입니다.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>A new &lt;color=#00B9FF&gt;Rank 7 Permit&lt;/color&gt; has been issued.
+You may now enter &lt;color=#B0FF06&gt;밀물 동굴&lt;/color&gt;.
+Recommended level: &lt;color=#FFFF00&gt;73&lt;/color&gt; or higher.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>다음 &lt;#00B9FF&gt;[&lt;#858585&gt;8&lt;/color&gt;]급&lt;/color&gt;으로 진급하시려면
+[&lt;#2DFF00&gt;&lt;b&gt;멧돼지 가죽&lt;/b&gt;&lt;/color&gt;] &lt;#2DFF00&gt;&lt;b&gt;9&lt;/b&gt;&lt;/color&gt;개가 필요합니다.
+[&lt;#B0FF06&gt;밀물 동굴&lt;/color&gt;]에 서식하는 마물에게서 얻으실 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>To reach &lt;color=#00B9FF&gt;rank 8&lt;/color&gt;,
+you will need &lt;color=#2DFF00&gt;&lt;b&gt;9&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;멧돼지 가죽&lt;/b&gt;&lt;/color&gt;.
+They drop from the creatures of &lt;color=#B0FF06&gt;밀물 동굴&lt;/color&gt;.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>그럼 다녀오신 뒤에 다시 뵙죠.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Then I’ll see you when you return.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>TextKey</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Kor</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Eng</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>다시 오셨군요,
+[&lt;#2DFF00&gt;&lt;b&gt;멧돼지 가죽&lt;/b&gt;&lt;/color&gt;] &lt;#2DFF00&gt;&lt;b&gt;9&lt;/b&gt;&lt;/color&gt;개는 구해오셨나요?</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Back again.
+Did you bring &lt;color=#2DFF00&gt;&lt;b&gt;9&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;멧돼지 가죽&lt;/b&gt;&lt;/color&gt;?</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>….
+확인 되었습니다.
+협회 규정에 따라
+&lt;#00B9FF&gt;[&lt;#858585&gt;8&lt;/color&gt;]급 모험가&lt;/color&gt; 승급을 진행하겠습니다.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>...Confirmed.
+In accordance with guild regulations,
+your promotion to a &lt;color=#00B9FF&gt;[&lt;color=#858585&gt;8&lt;/color&gt;]-rank Adventurer&lt;/color&gt; will now proceed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>&lt;#00B9FF&gt;[&lt;#858585&gt;8&lt;/color&gt;]급 통행증&lt;/color&gt;을 새로 발급해 드렸습니다.
+이제 [&lt;#B0FF06&gt;부서진 잔교&lt;/color&gt;]까지 출입하실 수 있습니다.
+권장 수준은 &lt;#FFFF00&gt;85&lt;/color&gt; 이상입니다.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>A new &lt;color=#00B9FF&gt;Rank 8 Permit&lt;/color&gt; has been issued.
+You may now enter &lt;color=#B0FF06&gt;부서진 잔교&lt;/color&gt;.
+Recommended level: &lt;color=#FFFF00&gt;85&lt;/color&gt; or higher.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>다음 &lt;#00B9FF&gt;[&lt;#858585&gt;9&lt;/color&gt;]급&lt;/color&gt;으로 진급하시려면
+[&lt;#2DFF00&gt;&lt;b&gt;거미 실크&lt;/b&gt;&lt;/color&gt;] &lt;#2DFF00&gt;&lt;b&gt;11&lt;/b&gt;&lt;/color&gt;개가 필요합니다.
+[&lt;#B0FF06&gt;부서진 잔교&lt;/color&gt;]에 서식하는 마물에게서 얻으실 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>To reach &lt;color=#00B9FF&gt;rank 9&lt;/color&gt;,
+you will need &lt;color=#2DFF00&gt;&lt;b&gt;11&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;거미 실크&lt;/b&gt;&lt;/color&gt;.
+They drop from the creatures of &lt;color=#B0FF06&gt;부서진 잔교&lt;/color&gt;.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>그럼 다녀오신 뒤에 다시 뵙죠.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Then I’ll see you when you return.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>TextKey</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Kor</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Eng</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>다시 오셨군요,
+[&lt;#2DFF00&gt;&lt;b&gt;거미 실크&lt;/b&gt;&lt;/color&gt;] &lt;#2DFF00&gt;&lt;b&gt;11&lt;/b&gt;&lt;/color&gt;개는 구해오셨나요?</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Back again.
+Did you bring &lt;color=#2DFF00&gt;&lt;b&gt;11&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;거미 실크&lt;/b&gt;&lt;/color&gt;?</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>….
+확인 되었습니다.
+협회 규정에 따라
+&lt;#00B9FF&gt;[&lt;#858585&gt;9&lt;/color&gt;]급 모험가&lt;/color&gt; 승급을 진행하겠습니다.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>...Confirmed.
+In accordance with guild regulations,
+your promotion to a &lt;color=#00B9FF&gt;[&lt;color=#858585&gt;9&lt;/color&gt;]-rank Adventurer&lt;/color&gt; will now proceed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>&lt;#00B9FF&gt;[&lt;#858585&gt;9&lt;/color&gt;]급 통행증&lt;/color&gt;을 새로 발급해 드렸습니다.
+이제 [&lt;#B0FF06&gt;폭풍 절벽&lt;/color&gt;]까지 출입하실 수 있습니다.
+권장 수준은 &lt;#FFFF00&gt;97&lt;/color&gt; 이상입니다.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>A new &lt;color=#00B9FF&gt;Rank 9 Permit&lt;/color&gt; has been issued.
+You may now enter &lt;color=#B0FF06&gt;폭풍 절벽&lt;/color&gt;.
+Recommended level: &lt;color=#FFFF00&gt;97&lt;/color&gt; or higher.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>다음 &lt;#00B9FF&gt;[&lt;#858585&gt;10&lt;/color&gt;]급&lt;/color&gt;으로 진급하시려면
+[&lt;#2DFF00&gt;&lt;b&gt;바람 정수&lt;/b&gt;&lt;/color&gt;] &lt;#2DFF00&gt;&lt;b&gt;11&lt;/b&gt;&lt;/color&gt;개가 필요합니다.
+[&lt;#B0FF06&gt;폭풍 절벽&lt;/color&gt;]에 서식하는 마물에게서 얻으실 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>To reach &lt;color=#00B9FF&gt;rank 10&lt;/color&gt;,
+you will need &lt;color=#2DFF00&gt;&lt;b&gt;11&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;바람 정수&lt;/b&gt;&lt;/color&gt;.
+They drop from the creatures of &lt;color=#B0FF06&gt;폭풍 절벽&lt;/color&gt;.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>그럼 다녀오신 뒤에 다시 뵙죠.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Then I’ll see you when you return.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>TextKey</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Kor</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Eng</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>다시 오셨군요,
+[&lt;#2DFF00&gt;&lt;b&gt;바람 정수&lt;/b&gt;&lt;/color&gt;] &lt;#2DFF00&gt;&lt;b&gt;11&lt;/b&gt;&lt;/color&gt;개는 구해오셨나요?</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Back again.
+Did you bring &lt;color=#2DFF00&gt;&lt;b&gt;11&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;바람 정수&lt;/b&gt;&lt;/color&gt;?</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>….
+확인 되었습니다.
+협회 규정에 따라
+&lt;#00B9FF&gt;[&lt;#858585&gt;10&lt;/color&gt;]급 모험가&lt;/color&gt; 승급을 진행하겠습니다.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>...Confirmed.
+In accordance with guild regulations,
+your promotion to a &lt;color=#00B9FF&gt;[&lt;color=#858585&gt;10&lt;/color&gt;]-rank Adventurer&lt;/color&gt; will now proceed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>&lt;#00B9FF&gt;[&lt;#858585&gt;10&lt;/color&gt;]급 통행증&lt;/color&gt;을 새로 발급해 드렸습니다.
+이제 [&lt;#B0FF06&gt;표류목 숲&lt;/color&gt;]까지 출입하실 수 있습니다.
+권장 수준은 &lt;#FFFF00&gt;109&lt;/color&gt; 이상입니다.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>A new &lt;color=#00B9FF&gt;Rank 10 Permit&lt;/color&gt; has been issued.
+You may now enter &lt;color=#B0FF06&gt;표류목 숲&lt;/color&gt;.
+Recommended level: &lt;color=#FFFF00&gt;109&lt;/color&gt; or higher.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>다음 &lt;#00B9FF&gt;[&lt;#858585&gt;11&lt;/color&gt;]급&lt;/color&gt;으로 진급하시려면
+[&lt;#2DFF00&gt;&lt;b&gt;그림자 응결물&lt;/b&gt;&lt;/color&gt;] &lt;#2DFF00&gt;&lt;b&gt;13&lt;/b&gt;&lt;/color&gt;개가 필요합니다.
+[&lt;#B0FF06&gt;표류목 숲&lt;/color&gt;]에 서식하는 마물에게서 얻으실 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>To reach &lt;color=#00B9FF&gt;rank 11&lt;/color&gt;,
+you will need &lt;color=#2DFF00&gt;&lt;b&gt;13&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;그림자 응결물&lt;/b&gt;&lt;/color&gt;.
+They drop from the creatures of &lt;color=#B0FF06&gt;표류목 숲&lt;/color&gt;.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>그럼 다녀오신 뒤에 다시 뵙죠.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Then I’ll see you when you return.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>TextKey</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Kor</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Eng</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>다시 오셨군요,
+[&lt;#2DFF00&gt;&lt;b&gt;그림자 응결물&lt;/b&gt;&lt;/color&gt;] &lt;#2DFF00&gt;&lt;b&gt;13&lt;/b&gt;&lt;/color&gt;개는 구해오셨나요?</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Back again.
+Did you bring &lt;color=#2DFF00&gt;&lt;b&gt;13&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;그림자 응결물&lt;/b&gt;&lt;/color&gt;?</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>….
+확인 되었습니다.
+협회 규정에 따라
+&lt;#00B9FF&gt;[&lt;#858585&gt;11&lt;/color&gt;]급 모험가&lt;/color&gt; 승급을 진행하겠습니다.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>...Confirmed.
+In accordance with guild regulations,
+your promotion to a &lt;color=#00B9FF&gt;[&lt;color=#858585&gt;11&lt;/color&gt;]-rank Adventurer&lt;/color&gt; will now proceed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>&lt;#00B9FF&gt;[&lt;#858585&gt;11&lt;/color&gt;]급 통행증&lt;/color&gt;을 새로 발급해 드렸습니다.
+이제 [&lt;#B0FF06&gt;잿불 구덩이&lt;/color&gt;]까지 출입하실 수 있습니다.
+권장 수준은 &lt;#FFFF00&gt;121&lt;/color&gt; 이상입니다.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>A new &lt;color=#00B9FF&gt;Rank 11 Permit&lt;/color&gt; has been issued.
+You may now enter &lt;color=#B0FF06&gt;잿불 구덩이&lt;/color&gt;.
+Recommended level: &lt;color=#FFFF00&gt;121&lt;/color&gt; or higher.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>다음 &lt;#00B9FF&gt;[&lt;#858585&gt;12&lt;/color&gt;]급&lt;/color&gt;으로 진급하시려면
+[&lt;#2DFF00&gt;&lt;b&gt;박쥐 날개막&lt;/b&gt;&lt;/color&gt;] &lt;#2DFF00&gt;&lt;b&gt;15&lt;/b&gt;&lt;/color&gt;개가 필요합니다.
+[&lt;#B0FF06&gt;잿불 구덩이&lt;/color&gt;]에 서식하는 마물에게서 얻으실 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>To reach &lt;color=#00B9FF&gt;rank 12&lt;/color&gt;,
+you will need &lt;color=#2DFF00&gt;&lt;b&gt;15&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;박쥐 날개막&lt;/b&gt;&lt;/color&gt;.
+They drop from the creatures of &lt;color=#B0FF06&gt;잿불 구덩이&lt;/color&gt;.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>그럼 다녀오신 뒤에 다시 뵙죠.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Then I’ll see you when you return.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>TextKey</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Kor</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Eng</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>다시 오셨군요,
+[&lt;#2DFF00&gt;&lt;b&gt;박쥐 날개막&lt;/b&gt;&lt;/color&gt;] &lt;#2DFF00&gt;&lt;b&gt;15&lt;/b&gt;&lt;/color&gt;개는 구해오셨나요?</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Back again.
+Did you bring &lt;color=#2DFF00&gt;&lt;b&gt;15&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;박쥐 날개막&lt;/b&gt;&lt;/color&gt;?</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>….
+확인 되었습니다.
+협회 규정에 따라
+&lt;#00B9FF&gt;[&lt;#858585&gt;12&lt;/color&gt;]급 모험가&lt;/color&gt; 승급을 진행하겠습니다.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>...Confirmed.
+In accordance with guild regulations,
+your promotion to a &lt;color=#00B9FF&gt;[&lt;color=#858585&gt;12&lt;/color&gt;]-rank Adventurer&lt;/color&gt; will now proceed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>&lt;#00B9FF&gt;[&lt;#858585&gt;12&lt;/color&gt;]급 통행증&lt;/color&gt;을 새로 발급해 드렸습니다.
+이제 [&lt;#B0FF06&gt;깊은 수직굴&lt;/color&gt;]까지 출입하실 수 있습니다.
+권장 수준은 &lt;#FFFF00&gt;133&lt;/color&gt; 이상입니다.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>A new &lt;color=#00B9FF&gt;Rank 12 Permit&lt;/color&gt; has been issued.
+You may now enter &lt;color=#B0FF06&gt;깊은 수직굴&lt;/color&gt;.
+Recommended level: &lt;color=#FFFF00&gt;133&lt;/color&gt; or higher.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>다음 &lt;#00B9FF&gt;[&lt;#858585&gt;13&lt;/color&gt;]급&lt;/color&gt;으로 진급하시려면
+[&lt;#2DFF00&gt;&lt;b&gt;수정 파편&lt;/b&gt;&lt;/color&gt;] &lt;#2DFF00&gt;&lt;b&gt;15&lt;/b&gt;&lt;/color&gt;개가 필요합니다.
+[&lt;#B0FF06&gt;깊은 수직굴&lt;/color&gt;]에 서식하는 마물에게서 얻으실 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>To reach &lt;color=#00B9FF&gt;rank 13&lt;/color&gt;,
+you will need &lt;color=#2DFF00&gt;&lt;b&gt;15&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;수정 파편&lt;/b&gt;&lt;/color&gt;.
+They drop from the creatures of &lt;color=#B0FF06&gt;깊은 수직굴&lt;/color&gt;.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>그럼 다녀오신 뒤에 다시 뵙죠.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Then I’ll see you when you return.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>TextKey</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Kor</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Eng</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>다시 오셨군요,
+[&lt;#2DFF00&gt;&lt;b&gt;수정 파편&lt;/b&gt;&lt;/color&gt;] &lt;#2DFF00&gt;&lt;b&gt;15&lt;/b&gt;&lt;/color&gt;개는 구해오셨나요?</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Back again.
+Did you bring &lt;color=#2DFF00&gt;&lt;b&gt;15&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;수정 파편&lt;/b&gt;&lt;/color&gt;?</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>….
+확인 되었습니다.
+협회 규정에 따라
+&lt;#00B9FF&gt;[&lt;#858585&gt;13&lt;/color&gt;]급 모험가&lt;/color&gt; 승급을 진행하겠습니다.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>...Confirmed.
+In accordance with guild regulations,
+your promotion to a &lt;color=#00B9FF&gt;[&lt;color=#858585&gt;13&lt;/color&gt;]-rank Adventurer&lt;/color&gt; will now proceed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>&lt;#00B9FF&gt;[&lt;#858585&gt;13&lt;/color&gt;]급 통행증&lt;/color&gt;을 새로 발급해 드렸습니다.
+이제 [&lt;#B0FF06&gt;녹슨 회랑&lt;/color&gt;]까지 출입하실 수 있습니다.
+권장 수준은 &lt;#FFFF00&gt;145&lt;/color&gt; 이상입니다.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>A new &lt;color=#00B9FF&gt;Rank 13 Permit&lt;/color&gt; has been issued.
+You may now enter &lt;color=#B0FF06&gt;녹슨 회랑&lt;/color&gt;.
+Recommended level: &lt;color=#FFFF00&gt;145&lt;/color&gt; or higher.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>다음 &lt;#00B9FF&gt;[&lt;#858585&gt;14&lt;/color&gt;]급&lt;/color&gt;으로 진급하시려면
+[&lt;#2DFF00&gt;&lt;b&gt;석상 조각&lt;/b&gt;&lt;/color&gt;] &lt;#2DFF00&gt;&lt;b&gt;17&lt;/b&gt;&lt;/color&gt;개가 필요합니다.
+[&lt;#B0FF06&gt;녹슨 회랑&lt;/color&gt;]에 서식하는 마물에게서 얻으실 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>To reach &lt;color=#00B9FF&gt;rank 14&lt;/color&gt;,
+you will need &lt;color=#2DFF00&gt;&lt;b&gt;17&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;석상 조각&lt;/b&gt;&lt;/color&gt;.
+They drop from the creatures of &lt;color=#B0FF06&gt;녹슨 회랑&lt;/color&gt;.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>그럼 다녀오신 뒤에 다시 뵙죠.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Then I’ll see you when you return.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>TextKey</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Kor</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Eng</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>다시 오셨군요,
+[&lt;#2DFF00&gt;&lt;b&gt;석상 조각&lt;/b&gt;&lt;/color&gt;] &lt;#2DFF00&gt;&lt;b&gt;17&lt;/b&gt;&lt;/color&gt;개는 구해오셨나요?</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Back again.
+Did you bring &lt;color=#2DFF00&gt;&lt;b&gt;17&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;석상 조각&lt;/b&gt;&lt;/color&gt;?</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>….
+확인 되었습니다.
+협회 규정에 따라
+&lt;#00B9FF&gt;[&lt;#858585&gt;14&lt;/color&gt;]급 모험가&lt;/color&gt; 승급을 진행하겠습니다.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>...Confirmed.
+In accordance with guild regulations,
+your promotion to a &lt;color=#00B9FF&gt;[&lt;color=#858585&gt;14&lt;/color&gt;]-rank Adventurer&lt;/color&gt; will now proceed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>&lt;#00B9FF&gt;[&lt;#858585&gt;14&lt;/color&gt;]급 통행증&lt;/color&gt;을 새로 발급해 드렸습니다.
+이제 [&lt;#B0FF06&gt;불씨 광맥&lt;/color&gt;]까지 출입하실 수 있습니다.
+권장 수준은 &lt;#FFFF00&gt;157&lt;/color&gt; 이상입니다.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>A new &lt;color=#00B9FF&gt;Rank 14 Permit&lt;/color&gt; has been issued.
+You may now enter &lt;color=#B0FF06&gt;불씨 광맥&lt;/color&gt;.
+Recommended level: &lt;color=#FFFF00&gt;157&lt;/color&gt; or higher.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>다음 &lt;#00B9FF&gt;[&lt;#858585&gt;15&lt;/color&gt;]급&lt;/color&gt;으로 진급하시려면
+[&lt;#2DFF00&gt;&lt;b&gt;광부의 유품&lt;/b&gt;&lt;/color&gt;] &lt;#2DFF00&gt;&lt;b&gt;17&lt;/b&gt;&lt;/color&gt;개가 필요합니다.
+[&lt;#B0FF06&gt;불씨 광맥&lt;/color&gt;]에 서식하는 마물에게서 얻으실 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>To reach &lt;color=#00B9FF&gt;rank 15&lt;/color&gt;,
+you will need &lt;color=#2DFF00&gt;&lt;b&gt;17&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;광부의 유품&lt;/b&gt;&lt;/color&gt;.
+They drop from the creatures of &lt;color=#B0FF06&gt;불씨 광맥&lt;/color&gt;.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>그럼 다녀오신 뒤에 다시 뵙죠.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Then I’ll see you when you return.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -701,6 +1935,1216 @@
 Here’s your very first &lt;#DE0000&gt;Recovery Potion&lt;/color&gt;♡
 Take good care of it~
 Make sure to sip it~ okay? heehee</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>TextKey</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Kor</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Eng</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>다시 오셨군요,
+[&lt;#2DFF00&gt;&lt;b&gt;광부의 유품&lt;/b&gt;&lt;/color&gt;] &lt;#2DFF00&gt;&lt;b&gt;17&lt;/b&gt;&lt;/color&gt;개는 구해오셨나요?</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Back again.
+Did you bring &lt;color=#2DFF00&gt;&lt;b&gt;17&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;광부의 유품&lt;/b&gt;&lt;/color&gt;?</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>….
+확인 되었습니다.
+협회 규정에 따라
+&lt;#00B9FF&gt;[&lt;#858585&gt;15&lt;/color&gt;]급 모험가&lt;/color&gt; 승급을 진행하겠습니다.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>...Confirmed.
+In accordance with guild regulations,
+your promotion to a &lt;color=#00B9FF&gt;[&lt;color=#858585&gt;15&lt;/color&gt;]-rank Adventurer&lt;/color&gt; will now proceed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>&lt;#00B9FF&gt;[&lt;#858585&gt;15&lt;/color&gt;]급 통행증&lt;/color&gt;을 새로 발급해 드렸습니다.
+이제 [&lt;#B0FF06&gt;무너진 갱도&lt;/color&gt;]까지 출입하실 수 있습니다.
+권장 수준은 &lt;#FFFF00&gt;169&lt;/color&gt; 이상입니다.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>A new &lt;color=#00B9FF&gt;Rank 15 Permit&lt;/color&gt; has been issued.
+You may now enter &lt;color=#B0FF06&gt;무너진 갱도&lt;/color&gt;.
+Recommended level: &lt;color=#FFFF00&gt;169&lt;/color&gt; or higher.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>다음 &lt;#00B9FF&gt;[&lt;#858585&gt;16&lt;/color&gt;]급&lt;/color&gt;으로 진급하시려면
+[&lt;#2DFF00&gt;&lt;b&gt;젖은 이끼&lt;/b&gt;&lt;/color&gt;] &lt;#2DFF00&gt;&lt;b&gt;19&lt;/b&gt;&lt;/color&gt;개가 필요합니다.
+[&lt;#B0FF06&gt;무너진 갱도&lt;/color&gt;]에 서식하는 마물에게서 얻으실 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>To reach &lt;color=#00B9FF&gt;rank 16&lt;/color&gt;,
+you will need &lt;color=#2DFF00&gt;&lt;b&gt;19&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;젖은 이끼&lt;/b&gt;&lt;/color&gt;.
+They drop from the creatures of &lt;color=#B0FF06&gt;무너진 갱도&lt;/color&gt;.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>그럼 다녀오신 뒤에 다시 뵙죠.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Then I’ll see you when you return.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>TextKey</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Kor</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Eng</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>다시 오셨군요,
+[&lt;#2DFF00&gt;&lt;b&gt;젖은 이끼&lt;/b&gt;&lt;/color&gt;] &lt;#2DFF00&gt;&lt;b&gt;19&lt;/b&gt;&lt;/color&gt;개는 구해오셨나요?</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Back again.
+Did you bring &lt;color=#2DFF00&gt;&lt;b&gt;19&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;젖은 이끼&lt;/b&gt;&lt;/color&gt;?</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>….
+확인 되었습니다.
+협회 규정에 따라
+&lt;#00B9FF&gt;[&lt;#858585&gt;16&lt;/color&gt;]급 모험가&lt;/color&gt; 승급을 진행하겠습니다.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>...Confirmed.
+In accordance with guild regulations,
+your promotion to a &lt;color=#00B9FF&gt;[&lt;color=#858585&gt;16&lt;/color&gt;]-rank Adventurer&lt;/color&gt; will now proceed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>&lt;#00B9FF&gt;[&lt;#858585&gt;16&lt;/color&gt;]급 통행증&lt;/color&gt;을 새로 발급해 드렸습니다.
+이제 [&lt;#B0FF06&gt;서리 수림&lt;/color&gt;]까지 출입하실 수 있습니다.
+권장 수준은 &lt;#FFFF00&gt;181&lt;/color&gt; 이상입니다.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>A new &lt;color=#00B9FF&gt;Rank 16 Permit&lt;/color&gt; has been issued.
+You may now enter &lt;color=#B0FF06&gt;서리 수림&lt;/color&gt;.
+Recommended level: &lt;color=#FFFF00&gt;181&lt;/color&gt; or higher.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>다음 &lt;#00B9FF&gt;[&lt;#858585&gt;17&lt;/color&gt;]급&lt;/color&gt;으로 진급하시려면
+[&lt;#2DFF00&gt;&lt;b&gt;박쥐 날개막&lt;/b&gt;&lt;/color&gt;] &lt;#2DFF00&gt;&lt;b&gt;21&lt;/b&gt;&lt;/color&gt;개가 필요합니다.
+[&lt;#B0FF06&gt;서리 수림&lt;/color&gt;]에 서식하는 마물에게서 얻으실 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>To reach &lt;color=#00B9FF&gt;rank 17&lt;/color&gt;,
+you will need &lt;color=#2DFF00&gt;&lt;b&gt;21&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;박쥐 날개막&lt;/b&gt;&lt;/color&gt;.
+They drop from the creatures of &lt;color=#B0FF06&gt;서리 수림&lt;/color&gt;.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>그럼 다녀오신 뒤에 다시 뵙죠.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Then I’ll see you when you return.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>TextKey</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Kor</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Eng</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>다시 오셨군요,
+[&lt;#2DFF00&gt;&lt;b&gt;박쥐 날개막&lt;/b&gt;&lt;/color&gt;] &lt;#2DFF00&gt;&lt;b&gt;21&lt;/b&gt;&lt;/color&gt;개는 구해오셨나요?</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Back again.
+Did you bring &lt;color=#2DFF00&gt;&lt;b&gt;21&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;박쥐 날개막&lt;/b&gt;&lt;/color&gt;?</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>….
+확인 되었습니다.
+협회 규정에 따라
+&lt;#00B9FF&gt;[&lt;#858585&gt;17&lt;/color&gt;]급 모험가&lt;/color&gt; 승급을 진행하겠습니다.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>...Confirmed.
+In accordance with guild regulations,
+your promotion to a &lt;color=#00B9FF&gt;[&lt;color=#858585&gt;17&lt;/color&gt;]-rank Adventurer&lt;/color&gt; will now proceed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>&lt;#00B9FF&gt;[&lt;#858585&gt;17&lt;/color&gt;]급 통행증&lt;/color&gt;을 새로 발급해 드렸습니다.
+이제 [&lt;#B0FF06&gt;빙하 동굴&lt;/color&gt;]까지 출입하실 수 있습니다.
+권장 수준은 &lt;#FFFF00&gt;193&lt;/color&gt; 이상입니다.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>A new &lt;color=#00B9FF&gt;Rank 17 Permit&lt;/color&gt; has been issued.
+You may now enter &lt;color=#B0FF06&gt;빙하 동굴&lt;/color&gt;.
+Recommended level: &lt;color=#FFFF00&gt;193&lt;/color&gt; or higher.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>다음 &lt;#00B9FF&gt;[&lt;#858585&gt;18&lt;/color&gt;]급&lt;/color&gt;으로 진급하시려면
+[&lt;#2DFF00&gt;&lt;b&gt;두더지 발톱&lt;/b&gt;&lt;/color&gt;] &lt;#2DFF00&gt;&lt;b&gt;21&lt;/b&gt;&lt;/color&gt;개가 필요합니다.
+[&lt;#B0FF06&gt;빙하 동굴&lt;/color&gt;]에 서식하는 마물에게서 얻으실 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>To reach &lt;color=#00B9FF&gt;rank 18&lt;/color&gt;,
+you will need &lt;color=#2DFF00&gt;&lt;b&gt;21&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;두더지 발톱&lt;/b&gt;&lt;/color&gt;.
+They drop from the creatures of &lt;color=#B0FF06&gt;빙하 동굴&lt;/color&gt;.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>그럼 다녀오신 뒤에 다시 뵙죠.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Then I’ll see you when you return.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>TextKey</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Kor</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Eng</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>다시 오셨군요,
+[&lt;#2DFF00&gt;&lt;b&gt;두더지 발톱&lt;/b&gt;&lt;/color&gt;] &lt;#2DFF00&gt;&lt;b&gt;21&lt;/b&gt;&lt;/color&gt;개는 구해오셨나요?</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Back again.
+Did you bring &lt;color=#2DFF00&gt;&lt;b&gt;21&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;두더지 발톱&lt;/b&gt;&lt;/color&gt;?</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>….
+확인 되었습니다.
+협회 규정에 따라
+&lt;#00B9FF&gt;[&lt;#858585&gt;18&lt;/color&gt;]급 모험가&lt;/color&gt; 승급을 진행하겠습니다.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>...Confirmed.
+In accordance with guild regulations,
+your promotion to a &lt;color=#00B9FF&gt;[&lt;color=#858585&gt;18&lt;/color&gt;]-rank Adventurer&lt;/color&gt; will now proceed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>&lt;#00B9FF&gt;[&lt;#858585&gt;18&lt;/color&gt;]급 통행증&lt;/color&gt;을 새로 발급해 드렸습니다.
+이제 [&lt;#B0FF06&gt;고요한 예배당&lt;/color&gt;]까지 출입하실 수 있습니다.
+권장 수준은 &lt;#FFFF00&gt;205&lt;/color&gt; 이상입니다.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>A new &lt;color=#00B9FF&gt;Rank 18 Permit&lt;/color&gt; has been issued.
+You may now enter &lt;color=#B0FF06&gt;고요한 예배당&lt;/color&gt;.
+Recommended level: &lt;color=#FFFF00&gt;205&lt;/color&gt; or higher.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>다음 &lt;#00B9FF&gt;[&lt;#858585&gt;19&lt;/color&gt;]급&lt;/color&gt;으로 진급하시려면
+[&lt;#2DFF00&gt;&lt;b&gt;망령의 재&lt;/b&gt;&lt;/color&gt;] &lt;#2DFF00&gt;&lt;b&gt;23&lt;/b&gt;&lt;/color&gt;개가 필요합니다.
+[&lt;#B0FF06&gt;고요한 예배당&lt;/color&gt;]에 서식하는 마물에게서 얻으실 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>To reach &lt;color=#00B9FF&gt;rank 19&lt;/color&gt;,
+you will need &lt;color=#2DFF00&gt;&lt;b&gt;23&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;망령의 재&lt;/b&gt;&lt;/color&gt;.
+They drop from the creatures of &lt;color=#B0FF06&gt;고요한 예배당&lt;/color&gt;.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>그럼 다녀오신 뒤에 다시 뵙죠.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Then I’ll see you when you return.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>TextKey</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Kor</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Eng</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>다시 오셨군요,
+[&lt;#2DFF00&gt;&lt;b&gt;망령의 재&lt;/b&gt;&lt;/color&gt;] &lt;#2DFF00&gt;&lt;b&gt;23&lt;/b&gt;&lt;/color&gt;개는 구해오셨나요?</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Back again.
+Did you bring &lt;color=#2DFF00&gt;&lt;b&gt;23&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;망령의 재&lt;/b&gt;&lt;/color&gt;?</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>….
+확인 되었습니다.
+협회 규정에 따라
+&lt;#00B9FF&gt;[&lt;#858585&gt;19&lt;/color&gt;]급 모험가&lt;/color&gt; 승급을 진행하겠습니다.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>...Confirmed.
+In accordance with guild regulations,
+your promotion to a &lt;color=#00B9FF&gt;[&lt;color=#858585&gt;19&lt;/color&gt;]-rank Adventurer&lt;/color&gt; will now proceed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>&lt;#00B9FF&gt;[&lt;#858585&gt;19&lt;/color&gt;]급 통행증&lt;/color&gt;을 새로 발급해 드렸습니다.
+이제 [&lt;#B0FF06&gt;새하얀 황야&lt;/color&gt;]까지 출입하실 수 있습니다.
+권장 수준은 &lt;#FFFF00&gt;217&lt;/color&gt; 이상입니다.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>A new &lt;color=#00B9FF&gt;Rank 19 Permit&lt;/color&gt; has been issued.
+You may now enter &lt;color=#B0FF06&gt;새하얀 황야&lt;/color&gt;.
+Recommended level: &lt;color=#FFFF00&gt;217&lt;/color&gt; or higher.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>다음 &lt;#00B9FF&gt;[&lt;#858585&gt;20&lt;/color&gt;]급&lt;/color&gt;으로 진급하시려면
+[&lt;#2DFF00&gt;&lt;b&gt;기사의 문장&lt;/b&gt;&lt;/color&gt;] &lt;#2DFF00&gt;&lt;b&gt;23&lt;/b&gt;&lt;/color&gt;개가 필요합니다.
+[&lt;#B0FF06&gt;새하얀 황야&lt;/color&gt;]에 서식하는 마물에게서 얻으실 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>To reach &lt;color=#00B9FF&gt;rank 20&lt;/color&gt;,
+you will need &lt;color=#2DFF00&gt;&lt;b&gt;23&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;기사의 문장&lt;/b&gt;&lt;/color&gt;.
+They drop from the creatures of &lt;color=#B0FF06&gt;새하얀 황야&lt;/color&gt;.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>그럼 다녀오신 뒤에 다시 뵙죠.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Then I’ll see you when you return.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>TextKey</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Kor</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Eng</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>다시 오셨군요,
+[&lt;#2DFF00&gt;&lt;b&gt;기사의 문장&lt;/b&gt;&lt;/color&gt;] &lt;#2DFF00&gt;&lt;b&gt;23&lt;/b&gt;&lt;/color&gt;개는 구해오셨나요?</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Back again.
+Did you bring &lt;color=#2DFF00&gt;&lt;b&gt;23&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;기사의 문장&lt;/b&gt;&lt;/color&gt;?</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>….
+확인 되었습니다.
+협회 규정에 따라
+&lt;#00B9FF&gt;[&lt;#858585&gt;20&lt;/color&gt;]급 모험가&lt;/color&gt; 승급을 진행하겠습니다.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>...Confirmed.
+In accordance with guild regulations,
+your promotion to a &lt;color=#00B9FF&gt;[&lt;color=#858585&gt;20&lt;/color&gt;]-rank Adventurer&lt;/color&gt; will now proceed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>&lt;#00B9FF&gt;[&lt;#858585&gt;20&lt;/color&gt;]급 통행증&lt;/color&gt;을 새로 발급해 드렸습니다.
+이제 [&lt;#B0FF06&gt;얼어붙은 금고&lt;/color&gt;]까지 출입하실 수 있습니다.
+권장 수준은 &lt;#FFFF00&gt;229&lt;/color&gt; 이상입니다.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>A new &lt;color=#00B9FF&gt;Rank 20 Permit&lt;/color&gt; has been issued.
+You may now enter &lt;color=#B0FF06&gt;얼어붙은 금고&lt;/color&gt;.
+Recommended level: &lt;color=#FFFF00&gt;229&lt;/color&gt; or higher.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>다음 &lt;#00B9FF&gt;[&lt;#858585&gt;21&lt;/color&gt;]급&lt;/color&gt;으로 진급하시려면
+[&lt;#2DFF00&gt;&lt;b&gt;수호자의 핵&lt;/b&gt;&lt;/color&gt;] &lt;#2DFF00&gt;&lt;b&gt;25&lt;/b&gt;&lt;/color&gt;개가 필요합니다.
+[&lt;#B0FF06&gt;얼어붙은 금고&lt;/color&gt;]에 서식하는 마물에게서 얻으실 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>To reach &lt;color=#00B9FF&gt;rank 21&lt;/color&gt;,
+you will need &lt;color=#2DFF00&gt;&lt;b&gt;25&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;수호자의 핵&lt;/b&gt;&lt;/color&gt;.
+They drop from the creatures of &lt;color=#B0FF06&gt;얼어붙은 금고&lt;/color&gt;.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>그럼 다녀오신 뒤에 다시 뵙죠.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Then I’ll see you when you return.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>TextKey</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Kor</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Eng</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>다시 오셨군요,
+[&lt;#2DFF00&gt;&lt;b&gt;수호자의 핵&lt;/b&gt;&lt;/color&gt;] &lt;#2DFF00&gt;&lt;b&gt;25&lt;/b&gt;&lt;/color&gt;개는 구해오셨나요?</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Back again.
+Did you bring &lt;color=#2DFF00&gt;&lt;b&gt;25&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;수호자의 핵&lt;/b&gt;&lt;/color&gt;?</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>….
+확인 되었습니다.
+협회 규정에 따라
+&lt;#00B9FF&gt;[&lt;#858585&gt;21&lt;/color&gt;]급 모험가&lt;/color&gt; 승급을 진행하겠습니다.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>...Confirmed.
+In accordance with guild regulations,
+your promotion to a &lt;color=#00B9FF&gt;[&lt;color=#858585&gt;21&lt;/color&gt;]-rank Adventurer&lt;/color&gt; will now proceed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>&lt;#00B9FF&gt;[&lt;#858585&gt;21&lt;/color&gt;]급 통행증&lt;/color&gt;을 새로 발급해 드렸습니다.
+이제 [&lt;#B0FF06&gt;여명의 정원&lt;/color&gt;]까지 출입하실 수 있습니다.
+권장 수준은 &lt;#FFFF00&gt;241&lt;/color&gt; 이상입니다.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>A new &lt;color=#00B9FF&gt;Rank 21 Permit&lt;/color&gt; has been issued.
+You may now enter &lt;color=#B0FF06&gt;여명의 정원&lt;/color&gt;.
+Recommended level: &lt;color=#FFFF00&gt;241&lt;/color&gt; or higher.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>다음 &lt;#00B9FF&gt;[&lt;#858585&gt;22&lt;/color&gt;]급&lt;/color&gt;으로 진급하시려면
+[&lt;#2DFF00&gt;&lt;b&gt;망령의 재&lt;/b&gt;&lt;/color&gt;] &lt;#2DFF00&gt;&lt;b&gt;27&lt;/b&gt;&lt;/color&gt;개가 필요합니다.
+[&lt;#B0FF06&gt;여명의 정원&lt;/color&gt;]에 서식하는 마물에게서 얻으실 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>To reach &lt;color=#00B9FF&gt;rank 22&lt;/color&gt;,
+you will need &lt;color=#2DFF00&gt;&lt;b&gt;27&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;망령의 재&lt;/b&gt;&lt;/color&gt;.
+They drop from the creatures of &lt;color=#B0FF06&gt;여명의 정원&lt;/color&gt;.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>그럼 다녀오신 뒤에 다시 뵙죠.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Then I’ll see you when you return.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>TextKey</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Kor</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Eng</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>다시 오셨군요,
+[&lt;#2DFF00&gt;&lt;b&gt;망령의 재&lt;/b&gt;&lt;/color&gt;] &lt;#2DFF00&gt;&lt;b&gt;27&lt;/b&gt;&lt;/color&gt;개는 구해오셨나요?</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Back again.
+Did you bring &lt;color=#2DFF00&gt;&lt;b&gt;27&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;망령의 재&lt;/b&gt;&lt;/color&gt;?</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>….
+확인 되었습니다.
+협회 규정에 따라
+&lt;#00B9FF&gt;[&lt;#858585&gt;22&lt;/color&gt;]급 모험가&lt;/color&gt; 승급을 진행하겠습니다.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>...Confirmed.
+In accordance with guild regulations,
+your promotion to a &lt;color=#00B9FF&gt;[&lt;color=#858585&gt;22&lt;/color&gt;]-rank Adventurer&lt;/color&gt; will now proceed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>&lt;#00B9FF&gt;[&lt;#858585&gt;22&lt;/color&gt;]급 통행증&lt;/color&gt;을 새로 발급해 드렸습니다.
+이제 [&lt;#B0FF06&gt;공허의 계단&lt;/color&gt;]까지 출입하실 수 있습니다.
+권장 수준은 &lt;#FFFF00&gt;253&lt;/color&gt; 이상입니다.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>A new &lt;color=#00B9FF&gt;Rank 22 Permit&lt;/color&gt; has been issued.
+You may now enter &lt;color=#B0FF06&gt;공허의 계단&lt;/color&gt;.
+Recommended level: &lt;color=#FFFF00&gt;253&lt;/color&gt; or higher.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>다음 &lt;#00B9FF&gt;[&lt;#858585&gt;23&lt;/color&gt;]급&lt;/color&gt;으로 진급하시려면
+[&lt;#2DFF00&gt;&lt;b&gt;키메라 갈기&lt;/b&gt;&lt;/color&gt;] &lt;#2DFF00&gt;&lt;b&gt;27&lt;/b&gt;&lt;/color&gt;개가 필요합니다.
+[&lt;#B0FF06&gt;공허의 계단&lt;/color&gt;]에 서식하는 마물에게서 얻으실 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>To reach &lt;color=#00B9FF&gt;rank 23&lt;/color&gt;,
+you will need &lt;color=#2DFF00&gt;&lt;b&gt;27&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;키메라 갈기&lt;/b&gt;&lt;/color&gt;.
+They drop from the creatures of &lt;color=#B0FF06&gt;공허의 계단&lt;/color&gt;.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>그럼 다녀오신 뒤에 다시 뵙죠.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Then I’ll see you when you return.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>TextKey</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Kor</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Eng</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>다시 오셨군요,
+[&lt;#2DFF00&gt;&lt;b&gt;키메라 갈기&lt;/b&gt;&lt;/color&gt;] &lt;#2DFF00&gt;&lt;b&gt;27&lt;/b&gt;&lt;/color&gt;개는 구해오셨나요?</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Back again.
+Did you bring &lt;color=#2DFF00&gt;&lt;b&gt;27&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;키메라 갈기&lt;/b&gt;&lt;/color&gt;?</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>….
+확인 되었습니다.
+협회 규정에 따라
+&lt;#00B9FF&gt;[&lt;#858585&gt;23&lt;/color&gt;]급 모험가&lt;/color&gt; 승급을 진행하겠습니다.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>...Confirmed.
+In accordance with guild regulations,
+your promotion to a &lt;color=#00B9FF&gt;[&lt;color=#858585&gt;23&lt;/color&gt;]-rank Adventurer&lt;/color&gt; will now proceed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>&lt;#00B9FF&gt;[&lt;#858585&gt;23&lt;/color&gt;]급 통행증&lt;/color&gt;을 새로 발급해 드렸습니다.
+이제 [&lt;#B0FF06&gt;별의 성소&lt;/color&gt;]까지 출입하실 수 있습니다.
+권장 수준은 &lt;#FFFF00&gt;265&lt;/color&gt; 이상입니다.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>A new &lt;color=#00B9FF&gt;Rank 23 Permit&lt;/color&gt; has been issued.
+You may now enter &lt;color=#B0FF06&gt;별의 성소&lt;/color&gt;.
+Recommended level: &lt;color=#FFFF00&gt;265&lt;/color&gt; or higher.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>다음 &lt;#00B9FF&gt;[&lt;#858585&gt;24&lt;/color&gt;]급&lt;/color&gt;으로 진급하시려면
+[&lt;#2DFF00&gt;&lt;b&gt;기사의 문장&lt;/b&gt;&lt;/color&gt;] &lt;#2DFF00&gt;&lt;b&gt;29&lt;/b&gt;&lt;/color&gt;개가 필요합니다.
+[&lt;#B0FF06&gt;별의 성소&lt;/color&gt;]에 서식하는 마물에게서 얻으실 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>To reach &lt;color=#00B9FF&gt;rank 24&lt;/color&gt;,
+you will need &lt;color=#2DFF00&gt;&lt;b&gt;29&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;기사의 문장&lt;/b&gt;&lt;/color&gt;.
+They drop from the creatures of &lt;color=#B0FF06&gt;별의 성소&lt;/color&gt;.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>그럼 다녀오신 뒤에 다시 뵙죠.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Then I’ll see you when you return.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>TextKey</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Kor</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Eng</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>다시 오셨군요,
+[&lt;#2DFF00&gt;&lt;b&gt;기사의 문장&lt;/b&gt;&lt;/color&gt;] &lt;#2DFF00&gt;&lt;b&gt;29&lt;/b&gt;&lt;/color&gt;개는 구해오셨나요?</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Back again.
+Did you bring &lt;color=#2DFF00&gt;&lt;b&gt;29&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;기사의 문장&lt;/b&gt;&lt;/color&gt;?</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>….
+확인 되었습니다.
+협회 규정에 따라
+&lt;#00B9FF&gt;[&lt;#858585&gt;24&lt;/color&gt;]급 모험가&lt;/color&gt; 승급을 진행하겠습니다.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>...Confirmed.
+In accordance with guild regulations,
+your promotion to a &lt;color=#00B9FF&gt;[&lt;color=#858585&gt;24&lt;/color&gt;]-rank Adventurer&lt;/color&gt; will now proceed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>&lt;#00B9FF&gt;[&lt;#858585&gt;24&lt;/color&gt;]급 통행증&lt;/color&gt;을 새로 발급해 드렸습니다.
+이제 [&lt;#B0FF06&gt;마지막 성벽&lt;/color&gt;]까지 출입하실 수 있습니다.
+권장 수준은 &lt;#FFFF00&gt;277&lt;/color&gt; 이상입니다.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>A new &lt;color=#00B9FF&gt;Rank 24 Permit&lt;/color&gt; has been issued.
+You may now enter &lt;color=#B0FF06&gt;마지막 성벽&lt;/color&gt;.
+Recommended level: &lt;color=#FFFF00&gt;277&lt;/color&gt; or higher.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>다음 &lt;#00B9FF&gt;[&lt;#858585&gt;25&lt;/color&gt;]급&lt;/color&gt;으로 진급하시려면
+[&lt;#2DFF00&gt;&lt;b&gt;수호자의 핵&lt;/b&gt;&lt;/color&gt;] &lt;#2DFF00&gt;&lt;b&gt;29&lt;/b&gt;&lt;/color&gt;개가 필요합니다.
+[&lt;#B0FF06&gt;마지막 성벽&lt;/color&gt;]에 서식하는 마물에게서 얻으실 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>To reach &lt;color=#00B9FF&gt;rank 25&lt;/color&gt;,
+you will need &lt;color=#2DFF00&gt;&lt;b&gt;29&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;수호자의 핵&lt;/b&gt;&lt;/color&gt;.
+They drop from the creatures of &lt;color=#B0FF06&gt;마지막 성벽&lt;/color&gt;.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>그럼 다녀오신 뒤에 다시 뵙죠.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Then I’ll see you when you return.</t>
         </is>
       </c>
     </row>
@@ -802,6 +3246,244 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>TextKey</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Kor</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Eng</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>다시 오셨군요,
+[&lt;#2DFF00&gt;&lt;b&gt;수호자의 핵&lt;/b&gt;&lt;/color&gt;] &lt;#2DFF00&gt;&lt;b&gt;29&lt;/b&gt;&lt;/color&gt;개는 구해오셨나요?</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Back again.
+Did you bring &lt;color=#2DFF00&gt;&lt;b&gt;29&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;수호자의 핵&lt;/b&gt;&lt;/color&gt;?</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>….
+확인 되었습니다.
+협회 규정에 따라
+&lt;#00B9FF&gt;[&lt;#858585&gt;25&lt;/color&gt;]급 모험가&lt;/color&gt; 승급을 진행하겠습니다.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>...Confirmed.
+In accordance with guild regulations,
+your promotion to a &lt;color=#00B9FF&gt;[&lt;color=#858585&gt;25&lt;/color&gt;]-rank Adventurer&lt;/color&gt; will now proceed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>&lt;#00B9FF&gt;[&lt;#858585&gt;25&lt;/color&gt;]급 통행증&lt;/color&gt;을 새로 발급해 드렸습니다.
+이제 [&lt;#B0FF06&gt;여명의 왕좌&lt;/color&gt;]까지 출입하실 수 있습니다.
+권장 수준은 &lt;#FFFF00&gt;289&lt;/color&gt; 이상입니다.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>A new &lt;color=#00B9FF&gt;Rank 25 Permit&lt;/color&gt; has been issued.
+You may now enter &lt;color=#B0FF06&gt;여명의 왕좌&lt;/color&gt;.
+Recommended level: &lt;color=#FFFF00&gt;289&lt;/color&gt; or higher.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>다음 &lt;#00B9FF&gt;[&lt;#858585&gt;26&lt;/color&gt;]급&lt;/color&gt;으로 진급하시려면
+[&lt;#2DFF00&gt;&lt;b&gt;망령의 재&lt;/b&gt;&lt;/color&gt;] &lt;#2DFF00&gt;&lt;b&gt;31&lt;/b&gt;&lt;/color&gt;개가 필요합니다.
+[&lt;#B0FF06&gt;여명의 왕좌&lt;/color&gt;]에 서식하는 마물에게서 얻으실 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>To reach &lt;color=#00B9FF&gt;rank 26&lt;/color&gt;,
+you will need &lt;color=#2DFF00&gt;&lt;b&gt;31&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;망령의 재&lt;/b&gt;&lt;/color&gt;.
+They drop from the creatures of &lt;color=#B0FF06&gt;여명의 왕좌&lt;/color&gt;.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>그럼 다녀오신 뒤에 다시 뵙죠.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Then I’ll see you when you return.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>TextKey</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Kor</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Eng</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>다시 오셨군요,
+[&lt;#2DFF00&gt;&lt;b&gt;망령의 재&lt;/b&gt;&lt;/color&gt;] &lt;#2DFF00&gt;&lt;b&gt;31&lt;/b&gt;&lt;/color&gt;개는 구해오셨나요?</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Back again.
+Did you bring &lt;color=#2DFF00&gt;&lt;b&gt;31&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;망령의 재&lt;/b&gt;&lt;/color&gt;?</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>….
+확인 되었습니다.
+협회 규정에 따라
+&lt;#00B9FF&gt;[&lt;#858585&gt;26&lt;/color&gt;]급 모험가&lt;/color&gt; 승급을 진행하겠습니다.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>...Confirmed.
+In accordance with guild regulations,
+your promotion to a &lt;color=#00B9FF&gt;[&lt;color=#858585&gt;26&lt;/color&gt;]-rank Adventurer&lt;/color&gt; will now proceed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>&lt;#00B9FF&gt;[&lt;#858585&gt;26&lt;/color&gt;]급 모험가&lt;/color&gt; — 협회가 인정하는 최고 등급이십니다.
+모든 지역의 통행이 허가되었습니다.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>&lt;color=#00B9FF&gt;[&lt;color=#858585&gt;26&lt;/color&gt;]-rank Adventurer&lt;/color&gt; — the highest rank the guild recognises.
+Passage to every region has been granted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>여기까지가 협회가 준비한 마지막 임무입니다.
+그동안 수고 많으셨습니다.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>That was the last commission the guild had prepared.
+Thank you for your service.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>언제든 다시 들러 주세요.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Do drop by anytime.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -1204,16 +3886,16 @@
       <c r="B5" t="inlineStr">
         <is>
           <t>&lt;#00B9FF&gt;[&lt;#858585&gt;2&lt;/color&gt;]급 모험가&lt;/color&gt;로 승급되신 것을 축하드립니다.
-상위 등급의 임무와 새로운 지역 출입 허가는
-협회에서 준비 중입니다.</t>
+이어서 [&lt;#B0FF06&gt;속삭이는 동굴&lt;/color&gt;]로의 출입이 허가되었으며,
+다음 &lt;#00B9FF&gt;[&lt;#858585&gt;3&lt;/color&gt;]급&lt;/color&gt;으로 진급하시려면
+[&lt;#2DFF00&gt;&lt;b&gt;슬라임 젤리&lt;/b&gt;&lt;/color&gt;] &lt;#2DFF00&gt;&lt;b&gt;3&lt;/b&gt;&lt;/color&gt;개가 필요합니다.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Congratulations on your promotion to a
-&lt;color=#00B9FF&gt;[&lt;color=#858585&gt;2&lt;/color&gt;]-rank Adventurer&lt;/color&gt;.
-Higher-rank commissions and access to
-new regions are being prepared by the guild.</t>
+          <t>Congratulations on your promotion to a &lt;color=#00B9FF&gt;[&lt;color=#858585&gt;2&lt;/color&gt;]-rank Adventurer&lt;/color&gt;.
+Access to &lt;color=#B0FF06&gt;속삭이는 동굴&lt;/color&gt; has been granted.
+To reach &lt;color=#00B9FF&gt;rank 3&lt;/color&gt;, you will need &lt;color=#2DFF00&gt;&lt;b&gt;3&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;슬라임 젤리&lt;/b&gt;&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -1312,4 +3994,246 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>TextKey</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Kor</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Eng</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>다시 오셨군요,
+[&lt;#2DFF00&gt;&lt;b&gt;슬라임 젤리&lt;/b&gt;&lt;/color&gt;] &lt;#2DFF00&gt;&lt;b&gt;3&lt;/b&gt;&lt;/color&gt;개는 구해오셨나요?</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Back again.
+Did you bring &lt;color=#2DFF00&gt;&lt;b&gt;3&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;슬라임 젤리&lt;/b&gt;&lt;/color&gt;?</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>….
+확인 되었습니다.
+협회 규정에 따라
+&lt;#00B9FF&gt;[&lt;#858585&gt;3&lt;/color&gt;]급 모험가&lt;/color&gt; 승급을 진행하겠습니다.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>...Confirmed.
+In accordance with guild regulations,
+your promotion to a &lt;color=#00B9FF&gt;[&lt;color=#858585&gt;3&lt;/color&gt;]-rank Adventurer&lt;/color&gt; will now proceed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>&lt;#00B9FF&gt;[&lt;#858585&gt;3&lt;/color&gt;]급 통행증&lt;/color&gt;을 새로 발급해 드렸습니다.
+이제 [&lt;#B0FF06&gt;폐허가 된 성소&lt;/color&gt;]까지 출입하실 수 있습니다.
+권장 수준은 &lt;#FFFF00&gt;25&lt;/color&gt; 이상입니다.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>A new &lt;color=#00B9FF&gt;Rank 3 Permit&lt;/color&gt; has been issued.
+You may now enter &lt;color=#B0FF06&gt;폐허가 된 성소&lt;/color&gt;.
+Recommended level: &lt;color=#FFFF00&gt;25&lt;/color&gt; or higher.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>다음 &lt;#00B9FF&gt;[&lt;#858585&gt;4&lt;/color&gt;]급&lt;/color&gt;으로 진급하시려면
+[&lt;#2DFF00&gt;&lt;b&gt;독버섯 갓&lt;/b&gt;&lt;/color&gt;] &lt;#2DFF00&gt;&lt;b&gt;5&lt;/b&gt;&lt;/color&gt;개가 필요합니다.
+[&lt;#B0FF06&gt;폐허가 된 성소&lt;/color&gt;]에 서식하는 마물에게서 얻으실 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>To reach &lt;color=#00B9FF&gt;rank 4&lt;/color&gt;,
+you will need &lt;color=#2DFF00&gt;&lt;b&gt;5&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;독버섯 갓&lt;/b&gt;&lt;/color&gt;.
+They drop from the creatures of &lt;color=#B0FF06&gt;폐허가 된 성소&lt;/color&gt;.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>그럼 다녀오신 뒤에 다시 뵙죠.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Then I’ll see you when you return.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>TextKey</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Kor</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Eng</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>다시 오셨군요,
+[&lt;#2DFF00&gt;&lt;b&gt;독버섯 갓&lt;/b&gt;&lt;/color&gt;] &lt;#2DFF00&gt;&lt;b&gt;5&lt;/b&gt;&lt;/color&gt;개는 구해오셨나요?</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Back again.
+Did you bring &lt;color=#2DFF00&gt;&lt;b&gt;5&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;독버섯 갓&lt;/b&gt;&lt;/color&gt;?</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>….
+확인 되었습니다.
+협회 규정에 따라
+&lt;#00B9FF&gt;[&lt;#858585&gt;4&lt;/color&gt;]급 모험가&lt;/color&gt; 승급을 진행하겠습니다.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>...Confirmed.
+In accordance with guild regulations,
+your promotion to a &lt;color=#00B9FF&gt;[&lt;color=#858585&gt;4&lt;/color&gt;]-rank Adventurer&lt;/color&gt; will now proceed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>&lt;#00B9FF&gt;[&lt;#858585&gt;4&lt;/color&gt;]급 통행증&lt;/color&gt;을 새로 발급해 드렸습니다.
+이제 [&lt;#B0FF06&gt;가라앉은 숲&lt;/color&gt;]까지 출입하실 수 있습니다.
+권장 수준은 &lt;#FFFF00&gt;37&lt;/color&gt; 이상입니다.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>A new &lt;color=#00B9FF&gt;Rank 4 Permit&lt;/color&gt; has been issued.
+You may now enter &lt;color=#B0FF06&gt;가라앉은 숲&lt;/color&gt;.
+Recommended level: &lt;color=#FFFF00&gt;37&lt;/color&gt; or higher.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>다음 &lt;#00B9FF&gt;[&lt;#858585&gt;5&lt;/color&gt;]급&lt;/color&gt;으로 진급하시려면
+[&lt;#2DFF00&gt;&lt;b&gt;까마귀 깃털&lt;/b&gt;&lt;/color&gt;] &lt;#2DFF00&gt;&lt;b&gt;5&lt;/b&gt;&lt;/color&gt;개가 필요합니다.
+[&lt;#B0FF06&gt;가라앉은 숲&lt;/color&gt;]에 서식하는 마물에게서 얻으실 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>To reach &lt;color=#00B9FF&gt;rank 5&lt;/color&gt;,
+you will need &lt;color=#2DFF00&gt;&lt;b&gt;5&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;까마귀 깃털&lt;/b&gt;&lt;/color&gt;.
+They drop from the creatures of &lt;color=#B0FF06&gt;가라앉은 숲&lt;/color&gt;.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>그럼 다녀오신 뒤에 다시 뵙죠.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Then I’ll see you when you return.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Assets/@Resources/Data/Excel/DialogueData.xlsx
+++ b/Assets/@Resources/Data/Excel/DialogueData.xlsx
@@ -38,6 +38,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GuildQuest25Text" sheetId="29" state="visible" r:id="rId29"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GuildQuest26Text" sheetId="30" state="visible" r:id="rId30"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GuildQuest27Text" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ForgeNormalText" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ShopNormalText" sheetId="33" state="visible" r:id="rId33"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3484,6 +3486,272 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>TextKey</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Kor</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Eng</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>불 앞은 뜨거워.
+용건 있으면 빨리 말해.</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>It's hot by the fire.
+Say your piece quickly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>재료만 가져와.
+모양은 내가 잡아 줄 테니까.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Just bring me the materials.
+I'll shape them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>쇠는 정직해.
+두드린 만큼만 단단해지지.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Iron is honest.
+It hardens exactly as much as you strike it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>그 무기, 날이 상했는데.
+손봐 줄까?</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>That blade's gone dull.
+Want me to work on it?</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>강화는 운이야.
+실패해도 나한테 화내지 마.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Enhancement is luck.
+Don't take a failure out on me.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>좋은 장비 하나가
+목숨을 두 번 살려.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>One good piece of gear
+saves your life twice.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>TextKey</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Kor</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Eng</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>어서 오세요!
+오늘은 뭘 찾으시나요?</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Welcome!
+What are you looking for today?</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>재료는 넉넉히 사 두세요.
+필요할 때는 꼭 모자라거든요.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Buy plenty of materials.
+You always run short right when you need them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>안 쓰는 물건은 저한테 파세요.
+값은 후하게 쳐 드릴게요… 조금은요.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Sell me what you don't use.
+I'll pay well... a little well.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>강화 주문서요?
+안쪽 선반에 있습니다.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Enhancement scrolls?
+They're on the inner shelf.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>골드는 쓰라고 있는 겁니다.
+쌓아두면 그냥 쇳조각이죠.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Gold is meant to be spent.
+Piled up, it's just scrap metal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>또 오세요!
+다음엔 더 좋은 물건 들여놓을게요.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Come again!
+I'll have better stock next time.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/Assets/@Resources/Data/Excel/DialogueData.xlsx
+++ b/Assets/@Resources/Data/Excel/DialogueData.xlsx
@@ -40,6 +40,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GuildQuest27Text" sheetId="31" state="visible" r:id="rId31"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ForgeNormalText" sheetId="32" state="visible" r:id="rId32"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ShopNormalText" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MonasteryNormalText" sheetId="34" state="visible" r:id="rId34"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3752,6 +3753,137 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>TextKey</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Kor</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Eng</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>먼 길 오셨군요.
+잠시 숨을 고르고 가세요.</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>You've come a long way.
+Rest and catch your breath a while.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>축성을 받으시겠습니까?
+길이 하나 더 열릴 것입니다.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Would you receive a blessing?
+Another path will open to you.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>힘은 쥐는 것이 아니라
+맡겨지는 것입니다.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Strength is not seized.
+It is entrusted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>당신이 벤 것들도
+한때는 살아 있었습니다.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>The things you have cut down
+were once alive, too.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>두려움은 죄가 아닙니다.
+멈추지 않으면 됩니다.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Fear is no sin.
+Only stopping is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>여기서는 무기를 내려놓으셔도 됩니다.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>You may set down your weapon here.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/Assets/@Resources/Data/Excel/DialogueData.xlsx
+++ b/Assets/@Resources/Data/Excel/DialogueData.xlsx
@@ -578,7 +578,7 @@
       <c r="C2" t="inlineStr">
         <is>
           <t>Back again.
-Did you bring &lt;color=#2DFF00&gt;&lt;b&gt;5&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;까마귀 깃털&lt;/b&gt;&lt;/color&gt;?</t>
+Did you bring &lt;color=#2DFF00&gt;&lt;b&gt;5&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;Crow Feathers&lt;/b&gt;&lt;/color&gt;?</t>
         </is>
       </c>
     </row>
@@ -616,7 +616,7 @@
       <c r="C4" t="inlineStr">
         <is>
           <t>A new &lt;color=#00B9FF&gt;Rank 5 Permit&lt;/color&gt; has been issued.
-You may now enter &lt;color=#B0FF06&gt;텅 빈 굴&lt;/color&gt;.
+You may now enter &lt;color=#B0FF06&gt;Hollow Burrow&lt;/color&gt;.
 Recommended level: &lt;color=#FFFF00&gt;49&lt;/color&gt; or higher.</t>
         </is>
       </c>
@@ -635,8 +635,8 @@
       <c r="C5" t="inlineStr">
         <is>
           <t>To reach &lt;color=#00B9FF&gt;rank 6&lt;/color&gt;,
-you will need &lt;color=#2DFF00&gt;&lt;b&gt;7&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;슬라임 젤리&lt;/b&gt;&lt;/color&gt;.
-They drop from the creatures of &lt;color=#B0FF06&gt;텅 빈 굴&lt;/color&gt;.</t>
+you will need &lt;color=#2DFF00&gt;&lt;b&gt;7&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;Slime Jellies&lt;/b&gt;&lt;/color&gt;.
+They drop from the creatures of &lt;color=#B0FF06&gt;Hollow Burrow&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       <c r="C2" t="inlineStr">
         <is>
           <t>Back again.
-Did you bring &lt;color=#2DFF00&gt;&lt;b&gt;7&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;슬라임 젤리&lt;/b&gt;&lt;/color&gt;?</t>
+Did you bring &lt;color=#2DFF00&gt;&lt;b&gt;7&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;Slime Jellies&lt;/b&gt;&lt;/color&gt;?</t>
         </is>
       </c>
     </row>
@@ -737,7 +737,7 @@
       <c r="C4" t="inlineStr">
         <is>
           <t>A new &lt;color=#00B9FF&gt;Rank 6 Permit&lt;/color&gt; has been issued.
-You may now enter &lt;color=#B0FF06&gt;소금 늪지&lt;/color&gt;.
+You may now enter &lt;color=#B0FF06&gt;Salt Marsh&lt;/color&gt;.
 Recommended level: &lt;color=#FFFF00&gt;61&lt;/color&gt; or higher.</t>
         </is>
       </c>
@@ -756,8 +756,8 @@
       <c r="C5" t="inlineStr">
         <is>
           <t>To reach &lt;color=#00B9FF&gt;rank 7&lt;/color&gt;,
-you will need &lt;color=#2DFF00&gt;&lt;b&gt;9&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;늑대 송곳니&lt;/b&gt;&lt;/color&gt;.
-They drop from the creatures of &lt;color=#B0FF06&gt;소금 늪지&lt;/color&gt;.</t>
+you will need &lt;color=#2DFF00&gt;&lt;b&gt;9&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;Wolf Fangs&lt;/b&gt;&lt;/color&gt;.
+They drop from the creatures of &lt;color=#B0FF06&gt;Salt Marsh&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       <c r="C2" t="inlineStr">
         <is>
           <t>Back again.
-Did you bring &lt;color=#2DFF00&gt;&lt;b&gt;9&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;늑대 송곳니&lt;/b&gt;&lt;/color&gt;?</t>
+Did you bring &lt;color=#2DFF00&gt;&lt;b&gt;9&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;Wolf Fangs&lt;/b&gt;&lt;/color&gt;?</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       <c r="C4" t="inlineStr">
         <is>
           <t>A new &lt;color=#00B9FF&gt;Rank 7 Permit&lt;/color&gt; has been issued.
-You may now enter &lt;color=#B0FF06&gt;밀물 동굴&lt;/color&gt;.
+You may now enter &lt;color=#B0FF06&gt;Tidal Cavern&lt;/color&gt;.
 Recommended level: &lt;color=#FFFF00&gt;73&lt;/color&gt; or higher.</t>
         </is>
       </c>
@@ -877,8 +877,8 @@
       <c r="C5" t="inlineStr">
         <is>
           <t>To reach &lt;color=#00B9FF&gt;rank 8&lt;/color&gt;,
-you will need &lt;color=#2DFF00&gt;&lt;b&gt;9&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;멧돼지 가죽&lt;/b&gt;&lt;/color&gt;.
-They drop from the creatures of &lt;color=#B0FF06&gt;밀물 동굴&lt;/color&gt;.</t>
+you will need &lt;color=#2DFF00&gt;&lt;b&gt;9&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;Boar Hides&lt;/b&gt;&lt;/color&gt;.
+They drop from the creatures of &lt;color=#B0FF06&gt;Tidal Cavern&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -941,7 +941,7 @@
       <c r="C2" t="inlineStr">
         <is>
           <t>Back again.
-Did you bring &lt;color=#2DFF00&gt;&lt;b&gt;9&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;멧돼지 가죽&lt;/b&gt;&lt;/color&gt;?</t>
+Did you bring &lt;color=#2DFF00&gt;&lt;b&gt;9&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;Boar Hides&lt;/b&gt;&lt;/color&gt;?</t>
         </is>
       </c>
     </row>
@@ -979,7 +979,7 @@
       <c r="C4" t="inlineStr">
         <is>
           <t>A new &lt;color=#00B9FF&gt;Rank 8 Permit&lt;/color&gt; has been issued.
-You may now enter &lt;color=#B0FF06&gt;부서진 잔교&lt;/color&gt;.
+You may now enter &lt;color=#B0FF06&gt;Broken Pier&lt;/color&gt;.
 Recommended level: &lt;color=#FFFF00&gt;85&lt;/color&gt; or higher.</t>
         </is>
       </c>
@@ -998,8 +998,8 @@
       <c r="C5" t="inlineStr">
         <is>
           <t>To reach &lt;color=#00B9FF&gt;rank 9&lt;/color&gt;,
-you will need &lt;color=#2DFF00&gt;&lt;b&gt;11&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;거미 실크&lt;/b&gt;&lt;/color&gt;.
-They drop from the creatures of &lt;color=#B0FF06&gt;부서진 잔교&lt;/color&gt;.</t>
+you will need &lt;color=#2DFF00&gt;&lt;b&gt;11&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;Spider Silk&lt;/b&gt;&lt;/color&gt;.
+They drop from the creatures of &lt;color=#B0FF06&gt;Broken Pier&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       <c r="C2" t="inlineStr">
         <is>
           <t>Back again.
-Did you bring &lt;color=#2DFF00&gt;&lt;b&gt;11&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;거미 실크&lt;/b&gt;&lt;/color&gt;?</t>
+Did you bring &lt;color=#2DFF00&gt;&lt;b&gt;11&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;Spider Silk&lt;/b&gt;&lt;/color&gt;?</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       <c r="C4" t="inlineStr">
         <is>
           <t>A new &lt;color=#00B9FF&gt;Rank 9 Permit&lt;/color&gt; has been issued.
-You may now enter &lt;color=#B0FF06&gt;폭풍 절벽&lt;/color&gt;.
+You may now enter &lt;color=#B0FF06&gt;Storm Cliff&lt;/color&gt;.
 Recommended level: &lt;color=#FFFF00&gt;97&lt;/color&gt; or higher.</t>
         </is>
       </c>
@@ -1119,8 +1119,8 @@
       <c r="C5" t="inlineStr">
         <is>
           <t>To reach &lt;color=#00B9FF&gt;rank 10&lt;/color&gt;,
-you will need &lt;color=#2DFF00&gt;&lt;b&gt;11&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;바람 정수&lt;/b&gt;&lt;/color&gt;.
-They drop from the creatures of &lt;color=#B0FF06&gt;폭풍 절벽&lt;/color&gt;.</t>
+you will need &lt;color=#2DFF00&gt;&lt;b&gt;11&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;Wind Essence&lt;/b&gt;&lt;/color&gt;.
+They drop from the creatures of &lt;color=#B0FF06&gt;Storm Cliff&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -1183,7 +1183,7 @@
       <c r="C2" t="inlineStr">
         <is>
           <t>Back again.
-Did you bring &lt;color=#2DFF00&gt;&lt;b&gt;11&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;바람 정수&lt;/b&gt;&lt;/color&gt;?</t>
+Did you bring &lt;color=#2DFF00&gt;&lt;b&gt;11&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;Wind Essence&lt;/b&gt;&lt;/color&gt;?</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1221,7 @@
       <c r="C4" t="inlineStr">
         <is>
           <t>A new &lt;color=#00B9FF&gt;Rank 10 Permit&lt;/color&gt; has been issued.
-You may now enter &lt;color=#B0FF06&gt;표류목 숲&lt;/color&gt;.
+You may now enter &lt;color=#B0FF06&gt;Driftwood Wood&lt;/color&gt;.
 Recommended level: &lt;color=#FFFF00&gt;109&lt;/color&gt; or higher.</t>
         </is>
       </c>
@@ -1240,8 +1240,8 @@
       <c r="C5" t="inlineStr">
         <is>
           <t>To reach &lt;color=#00B9FF&gt;rank 11&lt;/color&gt;,
-you will need &lt;color=#2DFF00&gt;&lt;b&gt;13&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;그림자 응결물&lt;/b&gt;&lt;/color&gt;.
-They drop from the creatures of &lt;color=#B0FF06&gt;표류목 숲&lt;/color&gt;.</t>
+you will need &lt;color=#2DFF00&gt;&lt;b&gt;13&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;Shadow Clots&lt;/b&gt;&lt;/color&gt;.
+They drop from the creatures of &lt;color=#B0FF06&gt;Driftwood Wood&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       <c r="C2" t="inlineStr">
         <is>
           <t>Back again.
-Did you bring &lt;color=#2DFF00&gt;&lt;b&gt;13&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;그림자 응결물&lt;/b&gt;&lt;/color&gt;?</t>
+Did you bring &lt;color=#2DFF00&gt;&lt;b&gt;13&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;Shadow Clots&lt;/b&gt;&lt;/color&gt;?</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
       <c r="C4" t="inlineStr">
         <is>
           <t>A new &lt;color=#00B9FF&gt;Rank 11 Permit&lt;/color&gt; has been issued.
-You may now enter &lt;color=#B0FF06&gt;잿불 구덩이&lt;/color&gt;.
+You may now enter &lt;color=#B0FF06&gt;Cinder Pit&lt;/color&gt;.
 Recommended level: &lt;color=#FFFF00&gt;121&lt;/color&gt; or higher.</t>
         </is>
       </c>
@@ -1361,8 +1361,8 @@
       <c r="C5" t="inlineStr">
         <is>
           <t>To reach &lt;color=#00B9FF&gt;rank 12&lt;/color&gt;,
-you will need &lt;color=#2DFF00&gt;&lt;b&gt;15&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;박쥐 날개막&lt;/b&gt;&lt;/color&gt;.
-They drop from the creatures of &lt;color=#B0FF06&gt;잿불 구덩이&lt;/color&gt;.</t>
+you will need &lt;color=#2DFF00&gt;&lt;b&gt;15&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;Bat Membranes&lt;/b&gt;&lt;/color&gt;.
+They drop from the creatures of &lt;color=#B0FF06&gt;Cinder Pit&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -1425,7 +1425,7 @@
       <c r="C2" t="inlineStr">
         <is>
           <t>Back again.
-Did you bring &lt;color=#2DFF00&gt;&lt;b&gt;15&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;박쥐 날개막&lt;/b&gt;&lt;/color&gt;?</t>
+Did you bring &lt;color=#2DFF00&gt;&lt;b&gt;15&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;Bat Membranes&lt;/b&gt;&lt;/color&gt;?</t>
         </is>
       </c>
     </row>
@@ -1463,7 +1463,7 @@
       <c r="C4" t="inlineStr">
         <is>
           <t>A new &lt;color=#00B9FF&gt;Rank 12 Permit&lt;/color&gt; has been issued.
-You may now enter &lt;color=#B0FF06&gt;깊은 수직굴&lt;/color&gt;.
+You may now enter &lt;color=#B0FF06&gt;Deep Shaft&lt;/color&gt;.
 Recommended level: &lt;color=#FFFF00&gt;133&lt;/color&gt; or higher.</t>
         </is>
       </c>
@@ -1482,8 +1482,8 @@
       <c r="C5" t="inlineStr">
         <is>
           <t>To reach &lt;color=#00B9FF&gt;rank 13&lt;/color&gt;,
-you will need &lt;color=#2DFF00&gt;&lt;b&gt;15&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;수정 파편&lt;/b&gt;&lt;/color&gt;.
-They drop from the creatures of &lt;color=#B0FF06&gt;깊은 수직굴&lt;/color&gt;.</t>
+you will need &lt;color=#2DFF00&gt;&lt;b&gt;15&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;Crystal Shards&lt;/b&gt;&lt;/color&gt;.
+They drop from the creatures of &lt;color=#B0FF06&gt;Deep Shaft&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       <c r="C2" t="inlineStr">
         <is>
           <t>Back again.
-Did you bring &lt;color=#2DFF00&gt;&lt;b&gt;15&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;수정 파편&lt;/b&gt;&lt;/color&gt;?</t>
+Did you bring &lt;color=#2DFF00&gt;&lt;b&gt;15&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;Crystal Shards&lt;/b&gt;&lt;/color&gt;?</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       <c r="C4" t="inlineStr">
         <is>
           <t>A new &lt;color=#00B9FF&gt;Rank 13 Permit&lt;/color&gt; has been issued.
-You may now enter &lt;color=#B0FF06&gt;녹슨 회랑&lt;/color&gt;.
+You may now enter &lt;color=#B0FF06&gt;Rust Hall&lt;/color&gt;.
 Recommended level: &lt;color=#FFFF00&gt;145&lt;/color&gt; or higher.</t>
         </is>
       </c>
@@ -1603,8 +1603,8 @@
       <c r="C5" t="inlineStr">
         <is>
           <t>To reach &lt;color=#00B9FF&gt;rank 14&lt;/color&gt;,
-you will need &lt;color=#2DFF00&gt;&lt;b&gt;17&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;석상 조각&lt;/b&gt;&lt;/color&gt;.
-They drop from the creatures of &lt;color=#B0FF06&gt;녹슨 회랑&lt;/color&gt;.</t>
+you will need &lt;color=#2DFF00&gt;&lt;b&gt;17&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;Statue Fragments&lt;/b&gt;&lt;/color&gt;.
+They drop from the creatures of &lt;color=#B0FF06&gt;Rust Hall&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -1667,7 +1667,7 @@
       <c r="C2" t="inlineStr">
         <is>
           <t>Back again.
-Did you bring &lt;color=#2DFF00&gt;&lt;b&gt;17&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;석상 조각&lt;/b&gt;&lt;/color&gt;?</t>
+Did you bring &lt;color=#2DFF00&gt;&lt;b&gt;17&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;Statue Fragments&lt;/b&gt;&lt;/color&gt;?</t>
         </is>
       </c>
     </row>
@@ -1705,7 +1705,7 @@
       <c r="C4" t="inlineStr">
         <is>
           <t>A new &lt;color=#00B9FF&gt;Rank 14 Permit&lt;/color&gt; has been issued.
-You may now enter &lt;color=#B0FF06&gt;불씨 광맥&lt;/color&gt;.
+You may now enter &lt;color=#B0FF06&gt;Ember Vein&lt;/color&gt;.
 Recommended level: &lt;color=#FFFF00&gt;157&lt;/color&gt; or higher.</t>
         </is>
       </c>
@@ -1724,8 +1724,8 @@
       <c r="C5" t="inlineStr">
         <is>
           <t>To reach &lt;color=#00B9FF&gt;rank 15&lt;/color&gt;,
-you will need &lt;color=#2DFF00&gt;&lt;b&gt;17&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;광부의 유품&lt;/b&gt;&lt;/color&gt;.
-They drop from the creatures of &lt;color=#B0FF06&gt;불씨 광맥&lt;/color&gt;.</t>
+you will need &lt;color=#2DFF00&gt;&lt;b&gt;17&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;Miner's Relics&lt;/b&gt;&lt;/color&gt;.
+They drop from the creatures of &lt;color=#B0FF06&gt;Ember Vein&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -1985,7 +1985,7 @@
       <c r="C2" t="inlineStr">
         <is>
           <t>Back again.
-Did you bring &lt;color=#2DFF00&gt;&lt;b&gt;17&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;광부의 유품&lt;/b&gt;&lt;/color&gt;?</t>
+Did you bring &lt;color=#2DFF00&gt;&lt;b&gt;17&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;Miner's Relics&lt;/b&gt;&lt;/color&gt;?</t>
         </is>
       </c>
     </row>
@@ -2023,7 +2023,7 @@
       <c r="C4" t="inlineStr">
         <is>
           <t>A new &lt;color=#00B9FF&gt;Rank 15 Permit&lt;/color&gt; has been issued.
-You may now enter &lt;color=#B0FF06&gt;무너진 갱도&lt;/color&gt;.
+You may now enter &lt;color=#B0FF06&gt;Collapsed Tunnel&lt;/color&gt;.
 Recommended level: &lt;color=#FFFF00&gt;169&lt;/color&gt; or higher.</t>
         </is>
       </c>
@@ -2042,8 +2042,8 @@
       <c r="C5" t="inlineStr">
         <is>
           <t>To reach &lt;color=#00B9FF&gt;rank 16&lt;/color&gt;,
-you will need &lt;color=#2DFF00&gt;&lt;b&gt;19&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;젖은 이끼&lt;/b&gt;&lt;/color&gt;.
-They drop from the creatures of &lt;color=#B0FF06&gt;무너진 갱도&lt;/color&gt;.</t>
+you will need &lt;color=#2DFF00&gt;&lt;b&gt;19&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;Damp Moss&lt;/b&gt;&lt;/color&gt;.
+They drop from the creatures of &lt;color=#B0FF06&gt;Collapsed Tunnel&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -2106,7 +2106,7 @@
       <c r="C2" t="inlineStr">
         <is>
           <t>Back again.
-Did you bring &lt;color=#2DFF00&gt;&lt;b&gt;19&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;젖은 이끼&lt;/b&gt;&lt;/color&gt;?</t>
+Did you bring &lt;color=#2DFF00&gt;&lt;b&gt;19&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;Damp Moss&lt;/b&gt;&lt;/color&gt;?</t>
         </is>
       </c>
     </row>
@@ -2144,7 +2144,7 @@
       <c r="C4" t="inlineStr">
         <is>
           <t>A new &lt;color=#00B9FF&gt;Rank 16 Permit&lt;/color&gt; has been issued.
-You may now enter &lt;color=#B0FF06&gt;서리 수림&lt;/color&gt;.
+You may now enter &lt;color=#B0FF06&gt;Frost Wood&lt;/color&gt;.
 Recommended level: &lt;color=#FFFF00&gt;181&lt;/color&gt; or higher.</t>
         </is>
       </c>
@@ -2163,8 +2163,8 @@
       <c r="C5" t="inlineStr">
         <is>
           <t>To reach &lt;color=#00B9FF&gt;rank 17&lt;/color&gt;,
-you will need &lt;color=#2DFF00&gt;&lt;b&gt;21&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;박쥐 날개막&lt;/b&gt;&lt;/color&gt;.
-They drop from the creatures of &lt;color=#B0FF06&gt;서리 수림&lt;/color&gt;.</t>
+you will need &lt;color=#2DFF00&gt;&lt;b&gt;21&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;Bat Membranes&lt;/b&gt;&lt;/color&gt;.
+They drop from the creatures of &lt;color=#B0FF06&gt;Frost Wood&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -2227,7 +2227,7 @@
       <c r="C2" t="inlineStr">
         <is>
           <t>Back again.
-Did you bring &lt;color=#2DFF00&gt;&lt;b&gt;21&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;박쥐 날개막&lt;/b&gt;&lt;/color&gt;?</t>
+Did you bring &lt;color=#2DFF00&gt;&lt;b&gt;21&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;Bat Membranes&lt;/b&gt;&lt;/color&gt;?</t>
         </is>
       </c>
     </row>
@@ -2265,7 +2265,7 @@
       <c r="C4" t="inlineStr">
         <is>
           <t>A new &lt;color=#00B9FF&gt;Rank 17 Permit&lt;/color&gt; has been issued.
-You may now enter &lt;color=#B0FF06&gt;빙하 동굴&lt;/color&gt;.
+You may now enter &lt;color=#B0FF06&gt;Glacier Cave&lt;/color&gt;.
 Recommended level: &lt;color=#FFFF00&gt;193&lt;/color&gt; or higher.</t>
         </is>
       </c>
@@ -2284,8 +2284,8 @@
       <c r="C5" t="inlineStr">
         <is>
           <t>To reach &lt;color=#00B9FF&gt;rank 18&lt;/color&gt;,
-you will need &lt;color=#2DFF00&gt;&lt;b&gt;21&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;두더지 발톱&lt;/b&gt;&lt;/color&gt;.
-They drop from the creatures of &lt;color=#B0FF06&gt;빙하 동굴&lt;/color&gt;.</t>
+you will need &lt;color=#2DFF00&gt;&lt;b&gt;21&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;Mole Claws&lt;/b&gt;&lt;/color&gt;.
+They drop from the creatures of &lt;color=#B0FF06&gt;Glacier Cave&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -2348,7 +2348,7 @@
       <c r="C2" t="inlineStr">
         <is>
           <t>Back again.
-Did you bring &lt;color=#2DFF00&gt;&lt;b&gt;21&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;두더지 발톱&lt;/b&gt;&lt;/color&gt;?</t>
+Did you bring &lt;color=#2DFF00&gt;&lt;b&gt;21&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;Mole Claws&lt;/b&gt;&lt;/color&gt;?</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       <c r="C4" t="inlineStr">
         <is>
           <t>A new &lt;color=#00B9FF&gt;Rank 18 Permit&lt;/color&gt; has been issued.
-You may now enter &lt;color=#B0FF06&gt;고요한 예배당&lt;/color&gt;.
+You may now enter &lt;color=#B0FF06&gt;Silent Chapel&lt;/color&gt;.
 Recommended level: &lt;color=#FFFF00&gt;205&lt;/color&gt; or higher.</t>
         </is>
       </c>
@@ -2405,8 +2405,8 @@
       <c r="C5" t="inlineStr">
         <is>
           <t>To reach &lt;color=#00B9FF&gt;rank 19&lt;/color&gt;,
-you will need &lt;color=#2DFF00&gt;&lt;b&gt;23&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;망령의 재&lt;/b&gt;&lt;/color&gt;.
-They drop from the creatures of &lt;color=#B0FF06&gt;고요한 예배당&lt;/color&gt;.</t>
+you will need &lt;color=#2DFF00&gt;&lt;b&gt;23&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;Revenant Ash&lt;/b&gt;&lt;/color&gt;.
+They drop from the creatures of &lt;color=#B0FF06&gt;Silent Chapel&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -2469,7 +2469,7 @@
       <c r="C2" t="inlineStr">
         <is>
           <t>Back again.
-Did you bring &lt;color=#2DFF00&gt;&lt;b&gt;23&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;망령의 재&lt;/b&gt;&lt;/color&gt;?</t>
+Did you bring &lt;color=#2DFF00&gt;&lt;b&gt;23&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;Revenant Ash&lt;/b&gt;&lt;/color&gt;?</t>
         </is>
       </c>
     </row>
@@ -2507,7 +2507,7 @@
       <c r="C4" t="inlineStr">
         <is>
           <t>A new &lt;color=#00B9FF&gt;Rank 19 Permit&lt;/color&gt; has been issued.
-You may now enter &lt;color=#B0FF06&gt;새하얀 황야&lt;/color&gt;.
+You may now enter &lt;color=#B0FF06&gt;White Waste&lt;/color&gt;.
 Recommended level: &lt;color=#FFFF00&gt;217&lt;/color&gt; or higher.</t>
         </is>
       </c>
@@ -2526,8 +2526,8 @@
       <c r="C5" t="inlineStr">
         <is>
           <t>To reach &lt;color=#00B9FF&gt;rank 20&lt;/color&gt;,
-you will need &lt;color=#2DFF00&gt;&lt;b&gt;23&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;기사의 문장&lt;/b&gt;&lt;/color&gt;.
-They drop from the creatures of &lt;color=#B0FF06&gt;새하얀 황야&lt;/color&gt;.</t>
+you will need &lt;color=#2DFF00&gt;&lt;b&gt;23&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;Knight's Crests&lt;/b&gt;&lt;/color&gt;.
+They drop from the creatures of &lt;color=#B0FF06&gt;White Waste&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="C2" t="inlineStr">
         <is>
           <t>Back again.
-Did you bring &lt;color=#2DFF00&gt;&lt;b&gt;23&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;기사의 문장&lt;/b&gt;&lt;/color&gt;?</t>
+Did you bring &lt;color=#2DFF00&gt;&lt;b&gt;23&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;Knight's Crests&lt;/b&gt;&lt;/color&gt;?</t>
         </is>
       </c>
     </row>
@@ -2628,7 +2628,7 @@
       <c r="C4" t="inlineStr">
         <is>
           <t>A new &lt;color=#00B9FF&gt;Rank 20 Permit&lt;/color&gt; has been issued.
-You may now enter &lt;color=#B0FF06&gt;얼어붙은 금고&lt;/color&gt;.
+You may now enter &lt;color=#B0FF06&gt;Frozen Vault&lt;/color&gt;.
 Recommended level: &lt;color=#FFFF00&gt;229&lt;/color&gt; or higher.</t>
         </is>
       </c>
@@ -2647,8 +2647,8 @@
       <c r="C5" t="inlineStr">
         <is>
           <t>To reach &lt;color=#00B9FF&gt;rank 21&lt;/color&gt;,
-you will need &lt;color=#2DFF00&gt;&lt;b&gt;25&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;수호자의 핵&lt;/b&gt;&lt;/color&gt;.
-They drop from the creatures of &lt;color=#B0FF06&gt;얼어붙은 금고&lt;/color&gt;.</t>
+you will need &lt;color=#2DFF00&gt;&lt;b&gt;25&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;Warden Cores&lt;/b&gt;&lt;/color&gt;.
+They drop from the creatures of &lt;color=#B0FF06&gt;Frozen Vault&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -2711,7 +2711,7 @@
       <c r="C2" t="inlineStr">
         <is>
           <t>Back again.
-Did you bring &lt;color=#2DFF00&gt;&lt;b&gt;25&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;수호자의 핵&lt;/b&gt;&lt;/color&gt;?</t>
+Did you bring &lt;color=#2DFF00&gt;&lt;b&gt;25&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;Warden Cores&lt;/b&gt;&lt;/color&gt;?</t>
         </is>
       </c>
     </row>
@@ -2749,7 +2749,7 @@
       <c r="C4" t="inlineStr">
         <is>
           <t>A new &lt;color=#00B9FF&gt;Rank 21 Permit&lt;/color&gt; has been issued.
-You may now enter &lt;color=#B0FF06&gt;여명의 정원&lt;/color&gt;.
+You may now enter &lt;color=#B0FF06&gt;Dawn Garden&lt;/color&gt;.
 Recommended level: &lt;color=#FFFF00&gt;241&lt;/color&gt; or higher.</t>
         </is>
       </c>
@@ -2768,8 +2768,8 @@
       <c r="C5" t="inlineStr">
         <is>
           <t>To reach &lt;color=#00B9FF&gt;rank 22&lt;/color&gt;,
-you will need &lt;color=#2DFF00&gt;&lt;b&gt;27&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;망령의 재&lt;/b&gt;&lt;/color&gt;.
-They drop from the creatures of &lt;color=#B0FF06&gt;여명의 정원&lt;/color&gt;.</t>
+you will need &lt;color=#2DFF00&gt;&lt;b&gt;27&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;Revenant Ash&lt;/b&gt;&lt;/color&gt;.
+They drop from the creatures of &lt;color=#B0FF06&gt;Dawn Garden&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -2832,7 +2832,7 @@
       <c r="C2" t="inlineStr">
         <is>
           <t>Back again.
-Did you bring &lt;color=#2DFF00&gt;&lt;b&gt;27&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;망령의 재&lt;/b&gt;&lt;/color&gt;?</t>
+Did you bring &lt;color=#2DFF00&gt;&lt;b&gt;27&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;Revenant Ash&lt;/b&gt;&lt;/color&gt;?</t>
         </is>
       </c>
     </row>
@@ -2870,7 +2870,7 @@
       <c r="C4" t="inlineStr">
         <is>
           <t>A new &lt;color=#00B9FF&gt;Rank 22 Permit&lt;/color&gt; has been issued.
-You may now enter &lt;color=#B0FF06&gt;공허의 계단&lt;/color&gt;.
+You may now enter &lt;color=#B0FF06&gt;Void Stair&lt;/color&gt;.
 Recommended level: &lt;color=#FFFF00&gt;253&lt;/color&gt; or higher.</t>
         </is>
       </c>
@@ -2889,8 +2889,8 @@
       <c r="C5" t="inlineStr">
         <is>
           <t>To reach &lt;color=#00B9FF&gt;rank 23&lt;/color&gt;,
-you will need &lt;color=#2DFF00&gt;&lt;b&gt;27&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;키메라 갈기&lt;/b&gt;&lt;/color&gt;.
-They drop from the creatures of &lt;color=#B0FF06&gt;공허의 계단&lt;/color&gt;.</t>
+you will need &lt;color=#2DFF00&gt;&lt;b&gt;27&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;Chimera Manes&lt;/b&gt;&lt;/color&gt;.
+They drop from the creatures of &lt;color=#B0FF06&gt;Void Stair&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2953,7 @@
       <c r="C2" t="inlineStr">
         <is>
           <t>Back again.
-Did you bring &lt;color=#2DFF00&gt;&lt;b&gt;27&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;키메라 갈기&lt;/b&gt;&lt;/color&gt;?</t>
+Did you bring &lt;color=#2DFF00&gt;&lt;b&gt;27&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;Chimera Manes&lt;/b&gt;&lt;/color&gt;?</t>
         </is>
       </c>
     </row>
@@ -2991,7 +2991,7 @@
       <c r="C4" t="inlineStr">
         <is>
           <t>A new &lt;color=#00B9FF&gt;Rank 23 Permit&lt;/color&gt; has been issued.
-You may now enter &lt;color=#B0FF06&gt;별의 성소&lt;/color&gt;.
+You may now enter &lt;color=#B0FF06&gt;Star Sanctum&lt;/color&gt;.
 Recommended level: &lt;color=#FFFF00&gt;265&lt;/color&gt; or higher.</t>
         </is>
       </c>
@@ -3010,8 +3010,8 @@
       <c r="C5" t="inlineStr">
         <is>
           <t>To reach &lt;color=#00B9FF&gt;rank 24&lt;/color&gt;,
-you will need &lt;color=#2DFF00&gt;&lt;b&gt;29&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;기사의 문장&lt;/b&gt;&lt;/color&gt;.
-They drop from the creatures of &lt;color=#B0FF06&gt;별의 성소&lt;/color&gt;.</t>
+you will need &lt;color=#2DFF00&gt;&lt;b&gt;29&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;Knight's Crests&lt;/b&gt;&lt;/color&gt;.
+They drop from the creatures of &lt;color=#B0FF06&gt;Star Sanctum&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -3074,7 +3074,7 @@
       <c r="C2" t="inlineStr">
         <is>
           <t>Back again.
-Did you bring &lt;color=#2DFF00&gt;&lt;b&gt;29&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;기사의 문장&lt;/b&gt;&lt;/color&gt;?</t>
+Did you bring &lt;color=#2DFF00&gt;&lt;b&gt;29&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;Knight's Crests&lt;/b&gt;&lt;/color&gt;?</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
       <c r="C4" t="inlineStr">
         <is>
           <t>A new &lt;color=#00B9FF&gt;Rank 24 Permit&lt;/color&gt; has been issued.
-You may now enter &lt;color=#B0FF06&gt;마지막 성벽&lt;/color&gt;.
+You may now enter &lt;color=#B0FF06&gt;Last Rampart&lt;/color&gt;.
 Recommended level: &lt;color=#FFFF00&gt;277&lt;/color&gt; or higher.</t>
         </is>
       </c>
@@ -3131,8 +3131,8 @@
       <c r="C5" t="inlineStr">
         <is>
           <t>To reach &lt;color=#00B9FF&gt;rank 25&lt;/color&gt;,
-you will need &lt;color=#2DFF00&gt;&lt;b&gt;29&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;수호자의 핵&lt;/b&gt;&lt;/color&gt;.
-They drop from the creatures of &lt;color=#B0FF06&gt;마지막 성벽&lt;/color&gt;.</t>
+you will need &lt;color=#2DFF00&gt;&lt;b&gt;29&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;Warden Cores&lt;/b&gt;&lt;/color&gt;.
+They drop from the creatures of &lt;color=#B0FF06&gt;Last Rampart&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -3288,7 +3288,7 @@
       <c r="C2" t="inlineStr">
         <is>
           <t>Back again.
-Did you bring &lt;color=#2DFF00&gt;&lt;b&gt;29&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;수호자의 핵&lt;/b&gt;&lt;/color&gt;?</t>
+Did you bring &lt;color=#2DFF00&gt;&lt;b&gt;29&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;Warden Cores&lt;/b&gt;&lt;/color&gt;?</t>
         </is>
       </c>
     </row>
@@ -3326,7 +3326,7 @@
       <c r="C4" t="inlineStr">
         <is>
           <t>A new &lt;color=#00B9FF&gt;Rank 25 Permit&lt;/color&gt; has been issued.
-You may now enter &lt;color=#B0FF06&gt;여명의 왕좌&lt;/color&gt;.
+You may now enter &lt;color=#B0FF06&gt;Throne of Dawn&lt;/color&gt;.
 Recommended level: &lt;color=#FFFF00&gt;289&lt;/color&gt; or higher.</t>
         </is>
       </c>
@@ -3345,8 +3345,8 @@
       <c r="C5" t="inlineStr">
         <is>
           <t>To reach &lt;color=#00B9FF&gt;rank 26&lt;/color&gt;,
-you will need &lt;color=#2DFF00&gt;&lt;b&gt;31&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;망령의 재&lt;/b&gt;&lt;/color&gt;.
-They drop from the creatures of &lt;color=#B0FF06&gt;여명의 왕좌&lt;/color&gt;.</t>
+you will need &lt;color=#2DFF00&gt;&lt;b&gt;31&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;Revenant Ash&lt;/b&gt;&lt;/color&gt;.
+They drop from the creatures of &lt;color=#B0FF06&gt;Throne of Dawn&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -3409,7 +3409,7 @@
       <c r="C2" t="inlineStr">
         <is>
           <t>Back again.
-Did you bring &lt;color=#2DFF00&gt;&lt;b&gt;31&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;망령의 재&lt;/b&gt;&lt;/color&gt;?</t>
+Did you bring &lt;color=#2DFF00&gt;&lt;b&gt;31&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;Revenant Ash&lt;/b&gt;&lt;/color&gt;?</t>
         </is>
       </c>
     </row>
@@ -4294,8 +4294,8 @@
       <c r="C5" t="inlineStr">
         <is>
           <t>Congratulations on your promotion to a &lt;color=#00B9FF&gt;[&lt;color=#858585&gt;2&lt;/color&gt;]-rank Adventurer&lt;/color&gt;.
-Access to &lt;color=#B0FF06&gt;속삭이는 동굴&lt;/color&gt; has been granted.
-To reach &lt;color=#00B9FF&gt;rank 3&lt;/color&gt;, you will need &lt;color=#2DFF00&gt;&lt;b&gt;3&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;슬라임 젤리&lt;/b&gt;&lt;/color&gt;.</t>
+Access to &lt;color=#B0FF06&gt;Whispering Cave&lt;/color&gt; has been granted.
+To reach &lt;color=#00B9FF&gt;rank 3&lt;/color&gt;, you will need &lt;color=#2DFF00&gt;&lt;b&gt;3&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;Slime Jellies&lt;/b&gt;&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -4435,7 +4435,7 @@
       <c r="C2" t="inlineStr">
         <is>
           <t>Back again.
-Did you bring &lt;color=#2DFF00&gt;&lt;b&gt;3&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;슬라임 젤리&lt;/b&gt;&lt;/color&gt;?</t>
+Did you bring &lt;color=#2DFF00&gt;&lt;b&gt;3&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;Slime Jellies&lt;/b&gt;&lt;/color&gt;?</t>
         </is>
       </c>
     </row>
@@ -4473,7 +4473,7 @@
       <c r="C4" t="inlineStr">
         <is>
           <t>A new &lt;color=#00B9FF&gt;Rank 3 Permit&lt;/color&gt; has been issued.
-You may now enter &lt;color=#B0FF06&gt;폐허가 된 성소&lt;/color&gt;.
+You may now enter &lt;color=#B0FF06&gt;Ruined Sanctum&lt;/color&gt;.
 Recommended level: &lt;color=#FFFF00&gt;25&lt;/color&gt; or higher.</t>
         </is>
       </c>
@@ -4492,8 +4492,8 @@
       <c r="C5" t="inlineStr">
         <is>
           <t>To reach &lt;color=#00B9FF&gt;rank 4&lt;/color&gt;,
-you will need &lt;color=#2DFF00&gt;&lt;b&gt;5&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;독버섯 갓&lt;/b&gt;&lt;/color&gt;.
-They drop from the creatures of &lt;color=#B0FF06&gt;폐허가 된 성소&lt;/color&gt;.</t>
+you will need &lt;color=#2DFF00&gt;&lt;b&gt;5&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;Toadstool Caps&lt;/b&gt;&lt;/color&gt;.
+They drop from the creatures of &lt;color=#B0FF06&gt;Ruined Sanctum&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -4556,7 +4556,7 @@
       <c r="C2" t="inlineStr">
         <is>
           <t>Back again.
-Did you bring &lt;color=#2DFF00&gt;&lt;b&gt;5&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;독버섯 갓&lt;/b&gt;&lt;/color&gt;?</t>
+Did you bring &lt;color=#2DFF00&gt;&lt;b&gt;5&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;Toadstool Caps&lt;/b&gt;&lt;/color&gt;?</t>
         </is>
       </c>
     </row>
@@ -4594,7 +4594,7 @@
       <c r="C4" t="inlineStr">
         <is>
           <t>A new &lt;color=#00B9FF&gt;Rank 4 Permit&lt;/color&gt; has been issued.
-You may now enter &lt;color=#B0FF06&gt;가라앉은 숲&lt;/color&gt;.
+You may now enter &lt;color=#B0FF06&gt;Sunken Grove&lt;/color&gt;.
 Recommended level: &lt;color=#FFFF00&gt;37&lt;/color&gt; or higher.</t>
         </is>
       </c>
@@ -4613,8 +4613,8 @@
       <c r="C5" t="inlineStr">
         <is>
           <t>To reach &lt;color=#00B9FF&gt;rank 5&lt;/color&gt;,
-you will need &lt;color=#2DFF00&gt;&lt;b&gt;5&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;까마귀 깃털&lt;/b&gt;&lt;/color&gt;.
-They drop from the creatures of &lt;color=#B0FF06&gt;가라앉은 숲&lt;/color&gt;.</t>
+you will need &lt;color=#2DFF00&gt;&lt;b&gt;5&lt;/b&gt;&lt;/color&gt; &lt;color=#2DFF00&gt;&lt;b&gt;Crow Feathers&lt;/b&gt;&lt;/color&gt;.
+They drop from the creatures of &lt;color=#B0FF06&gt;Sunken Grove&lt;/color&gt;.</t>
         </is>
       </c>
     </row>

--- a/Assets/@Resources/Data/Excel/DialogueData.xlsx
+++ b/Assets/@Resources/Data/Excel/DialogueData.xlsx
@@ -3240,7 +3240,9 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>I heard things have been a bit noisy\\naround Breezing Wind Forest lately.\\nDo be careful.</t>
+          <t>I heard things have been a bit noisy
+around Breezewood Forest lately.
+Do be careful.</t>
         </is>
       </c>
     </row>
@@ -4006,7 +4008,7 @@
       <c r="C7" t="inlineStr">
         <is>
           <t>The Pongs reside in the
-[&lt;#B0FF06&gt;Breezing Wind Forest&lt;/color&gt;]. 
+[&lt;#B0FF06&gt;Breezewood Forest&lt;/color&gt;]. 
 I'll grant you a [&lt;#00B9FF&gt;Temporary Permit&lt;/color&gt;].</t>
         </is>
       </c>

--- a/Assets/@Resources/Data/Excel/DialogueData.xlsx
+++ b/Assets/@Resources/Data/Excel/DialogueData.xlsx
@@ -4130,7 +4130,7 @@
         <is>
           <t>Furthermore, upon your promotion to a
 &lt;color=#00B9FF&gt;[&lt;color=#6F6F6F&gt;1&lt;/color&gt;]-rank Adventurer&lt;/color&gt;,
-access to the &lt;color=#B0FF06&gt;Breezing Wing Forest&lt;/color&gt;
+access to the &lt;color=#B0FF06&gt;Breezewood Forest&lt;/color&gt;
 has been granted, and the &lt;color=#00B9FF&gt;Alchemy&lt;/color&gt; is
 now available for use.</t>
         </is>
@@ -4172,7 +4172,7 @@
         <is>
           <t>Before you ask,
 to reach &lt;color=#00B9FF&gt;[&lt;color=#858585&gt;2&lt;/color&gt;]-rank Adventurer&lt;/color&gt;,
-you’ll need 5 &lt;color=#2DFF00&gt;&lt;b&gt;Bouncing Jelly&lt;/b&gt;&lt;/color&gt;.</t>
+you’ll need 5 &lt;color=#2DFF00&gt;&lt;b&gt;Rabijelly&lt;/b&gt;&lt;/color&gt;.</t>
         </is>
       </c>
     </row>

--- a/Assets/@Resources/Data/Excel/DialogueData.xlsx
+++ b/Assets/@Resources/Data/Excel/DialogueData.xlsx
@@ -41,6 +41,21 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ForgeNormalText" sheetId="32" state="visible" r:id="rId32"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ShopNormalText" sheetId="33" state="visible" r:id="rId33"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MonasteryNormalText" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BondReceptionist1Text" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BondReceptionist2Text" sheetId="36" state="visible" r:id="rId36"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BondReceptionist3Text" sheetId="37" state="visible" r:id="rId37"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BondAlchemist1Text" sheetId="38" state="visible" r:id="rId38"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BondAlchemist2Text" sheetId="39" state="visible" r:id="rId39"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BondAlchemist3Text" sheetId="40" state="visible" r:id="rId40"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BondBlacksmith1Text" sheetId="41" state="visible" r:id="rId41"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BondBlacksmith2Text" sheetId="42" state="visible" r:id="rId42"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BondBlacksmith3Text" sheetId="43" state="visible" r:id="rId43"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BondPriest1Text" sheetId="44" state="visible" r:id="rId44"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BondPriest2Text" sheetId="45" state="visible" r:id="rId45"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BondPriest3Text" sheetId="46" state="visible" r:id="rId46"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BondShopkeeper1Text" sheetId="47" state="visible" r:id="rId47"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BondShopkeeper2Text" sheetId="48" state="visible" r:id="rId48"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BondShopkeeper3Text" sheetId="49" state="visible" r:id="rId49"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3886,6 +3901,550 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>TextKey</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Kor</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Eng</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>…또 오셨군요.
+요즘은 오시는 게 반갑다고 해 두죠.</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>...You again.
+Let's say I'm glad to see you these days.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>협회 규정상 사적인 대화는 금지지만,
+잠깐이면 괜찮겠죠.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Guild rules forbid personal chats,
+but a moment should be fine.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>사실 이 일, 처음엔 사흘만 하고
+그만둘 생각이었어요.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Truth is, I meant to quit this job
+after three days.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>그런데 돌아오지 않은 모험가 명단을
+정리하다 보니… 그만둘 수가 없더군요.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Then I started filing the list of adventurers
+who never came back... and couldn't leave.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>그러니까 당신은 그 명단에 이름 올리지 마세요.
+서류가 늘어나니까요.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>So don't you end up on that list.
+It means more paperwork.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>TextKey</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Kor</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Eng</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>오늘은 제가 먼저 말을 걸죠.
+드문 일이니 기억해 두세요.</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Today I'll speak first.
+It's rare, so remember it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>제 책상 서랍엔 오래된 통행증이 하나 있어요.
+제 것이었죠.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>There's an old pass in my desk drawer.
+It was mine.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>저도 모험가였어요.
+산들바람 숲 너머까지는 못 갔지만요.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>I was an adventurer too.
+I never made it past Breezewood Forest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>그래서 당신이 새 통행증을 받아 갈 때마다
+조금 부럽기도 해요.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>So every time you take a new pass,
+I'm a little jealous.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>…방금 한 말은 서류에 남기지 마세요.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>...Don't put that in any report.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>TextKey</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Kor</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Eng</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>당신이 없는 동안
+협회가 너무 조용했어요.</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>The guild was far too quiet
+while you were away.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>규정집 어디에도 없지만,
+이건 제 개인 인장이에요.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>It's in no rulebook,
+but this is my personal seal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>이걸 찍은 서류는 제가 무조건 먼저
+처리해 드려요. 특별 대우죠.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Any form stamped with it goes to the top
+of my pile. Special treatment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>…고맙다는 말, 한 번만 할게요.
+늘 무사히 돌아와 줘서 고마워요.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>...I'll say thanks just once.
+Thank you for always coming back.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>자, 다음 임무 받으러 가시죠.
+제 모험가님.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Now, go get your next assignment.
+My adventurer.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>TextKey</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Kor</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Eng</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>어머~ 오늘은 물약 말고
+저를 보러 오신 거죠? 후훗♡</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Oh my~ You came to see me today,
+not a potion, right? Heehee♡</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>비밀 하나 알려 드릴게요.
+저, 쓴 약은 못 먹어요.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Here's a secret.
+I can't stand bitter medicine.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>그래서 제 물약엔 몰래 꿀을
+조금씩 넣어요. 다들 몰랐죠?</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>So I sneak a little honey into every potion.
+Nobody noticed, right?</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>당신 것엔 두 방울 넣어 드릴게요.
+특별 손님이니까요♡</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Yours gets two drops.
+You're a special customer♡</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>TextKey</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Kor</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Eng</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>요즘 새 물약을 연구하고 있어요.
+이름은… 아직 비밀♡</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>I'm working on a new potion lately.
+Its name is... a secret♡</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>스승님이 늘 말씀하셨어요.
+좋은 약은 마실 사람을 생각하며 만든다고.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>My teacher always said good medicine
+is made thinking of the one who drinks it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>그래서 요즘 자꾸 당신 생각을 하나 봐요.
+…연구 때문이에요, 연구!</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Maybe that's why I keep thinking of you.
+...For research, of course. Research!</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>완성되면 제일 먼저 맛보게 해 드릴게요.
+약속♡</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>When it's done, you'll be the first to taste it.
+Promise♡</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -4025,6 +4584,1011 @@
       <c r="C8" t="inlineStr">
         <is>
           <t>Then I’ll see you when you return.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>TextKey</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Kor</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Eng</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>짠~ 드디어 완성했어요!
+이름은 '돌아오는 길'이에요.</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Ta-da~ It's finally done!
+I call it 'The Way Back.'</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>효과요? 마시면 무슨 일이 있어도
+이 공방으로 돌아오고 싶어져요.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>The effect? Whoever drinks it
+will always want to come back here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>…농담이에요, 반쯤은요.
+나머지 반은 제 진심이고요♡</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>...I'm joking. Half joking.
+The other half is how I really feel♡</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>다치면 꼭 여기로 와요.
+제가 전부 고쳐 줄 테니까.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>If you ever get hurt, come straight here.
+I'll fix everything.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>후훗, 오늘은 공짜예요.
+대신 내일도 와야 해요?</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Heehee, today's on the house.
+But you have to come tomorrow too, okay?</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>TextKey</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Kor</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Eng</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>또 왔군. 앉아.
+불 좀 쬐고 가.</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Back again. Sit.
+Warm yourself by the fire.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>칼 자국을 보면 어떻게 싸우는지 보여.
+요즘 많이 늘었어.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Your blade's nicks tell me how you fight.
+You've gotten better.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>처음엔 막 휘두르기만 하더니,
+이젠 벨 곳을 알고 베는군.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>At first you just swung.
+Now you know where to cut.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>…칭찬이야.
+자주 안 하니까 잘 들어 둬.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>...That was praise.
+I don't give it often, so remember it.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>TextKey</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Kor</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Eng</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>이 망치, 우리 아버지 거야.</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>This hammer was my father's.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>아버진 기사단 무기를 만들었지.
+그 무기 든 기사들은 아무도 돌아오지 못했고.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>He forged for the knights.
+None of the knights who carried his blades came home.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>그래서 난 더 단단하게 두드려.
+들고 간 사람이 살아서 돌아오게.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>So I strike harder.
+So whoever carries my work comes back alive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>넌 매번 돌아오잖아.
+그게 내 망치질이 맞다는 증거야.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>You come back every time.
+That's proof my hammer's right.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>TextKey</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Kor</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Eng</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>받아.
+남은 쇳조각으로 만든 부적이야.</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Take this.
+A charm I made from leftover steel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>모양은 투박해도,
+내가 만든 것 중 제일 단단해.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>It's crude,
+but it's the toughest thing I've ever made.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>…너 주려고 만든 거 아니야.
+그냥 쇳조각이 남아서 만든 거야.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>...I didn't make it for you.
+Just had scraps left over.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>그래도 부러지면 가져와.
+몇 번이고 다시 만들어 줄 테니까.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>But if it breaks, bring it back.
+I'll make it again, as many times as it takes.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>TextKey</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Kor</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Eng</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>어서 오세요.
+오늘은 기도 대신 이야기를 나눌까요.</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Welcome.
+Shall we talk today instead of praying?</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>이 수도원의 종은 백 년 동안
+한 번도 멈춘 적이 없답니다.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>This monastery's bell hasn't stopped
+once in a hundred years.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>저는 매일 아침 그 종을 치며,
+떠난 이들이 돌아오기를 빌어요.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Every morning I ring it
+and pray for those who left to return.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>요즘은 그 기도에
+당신의 이름도 넣고 있습니다.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Lately,
+your name is in that prayer too.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>TextKey</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Kor</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Eng</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>고백하자면,
+저는 한때 칼을 들었던 사람입니다.</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>I confess,
+I once carried a sword.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>지키지 못한 것이 많아서,
+칼 대신 종을 잡았지요.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>I failed to protect too much,
+so I traded the blade for the bell.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>당신을 보면 그때의 제가 떠오릅니다.
+하지만 당신은 다르겠지요.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>You remind me of who I was.
+But you will be different.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>당신은 멈추지 않으니까요.
+두려워도 앞으로 가니까요.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Because you don't stop.
+Even afraid, you keep going.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>TextKey</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Kor</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Eng</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>오늘은 제가 당신을 위해
+축복을 올리겠습니다.</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Today I will offer
+a blessing for you.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>사람을 지키는 것은 힘이 아니라,
+돌아올 곳이 있다는 사실입니다.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>It is not strength that protects us,
+but having a place to return to.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>이 마을이, 그리고 이 수도원이
+당신의 돌아올 곳이 되기를.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>May this village, and this monastery,
+be yours to return to.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>…종소리가 들리면,
+제가 당신을 생각하고 있다는 뜻이에요.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>...When you hear the bell,
+know that I am thinking of you.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>TextKey</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Kor</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Eng</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>오, 단골손님!
+오늘은 구경만 해도 돼요. 특별히요.</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Oh, my regular!
+You can just browse today. As a favor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>장사에서 제일 중요한 게 뭔지 아세요?
+손님 얼굴 기억하기예요.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Know the most important thing in trade?
+Remembering faces.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>손님 얼굴은… 음,
+늘 흙투성이라 기억하기 쉬워요.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Yours is... well,
+always covered in dirt, so it's easy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>농담이에요!
+다음엔 좋은 물건 먼저 보여 드릴게요.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Just kidding!
+Next time you'll get first look at the good stuff.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>TextKey</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Kor</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Eng</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>사실 이 가게,
+원래는 제 할머니 가게였어요.</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Truth is,
+this shop was my grandmother's.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>할머니는 손해를 봐도
+모험가한테는 물약을 싸게 팔았죠.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>She sold potions cheap to adventurers,
+even at a loss.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>저는 장사꾼이라 그렇게는 못 하지만…
+당신한텐 조금 깎아 드릴게요.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>I'm a merchant, so I can't do that...
+but for you, a small discount.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>비밀이에요.
+다른 손님들이 알면 저 망해요!</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Keep it secret.
+If the others find out, I'm ruined!</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>TextKey</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Kor</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Eng</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>이거 받으세요.
+할머니 가게에서 제일 오래된 금화예요.</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Take this.
+The oldest gold coin from grandma's shop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>장사꾼이 돈을 그냥 주다니,
+저도 제가 믿기지 않네요.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>A merchant giving money away.
+I can't believe it myself.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>당신 덕분에 이 마을에 손님이 늘었어요.
+이건 투자예요, 투자!</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Thanks to you, this town has more customers.
+Call it an investment!</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>앞으로도 우리 가게
+제일 좋은 손님으로 남아 주세요.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Stay my very best customer,
+okay?</t>
         </is>
       </c>
     </row>
